--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/Melbourne Eats/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F206A0B1-9018-4261-B1F5-D759FC94C2CD}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF0EFF22-B412-4861-B0D6-67EC963AD0E0}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="143">
   <si>
     <t>San Telmo</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Vinesmith</t>
   </si>
   <si>
-    <t>Di Stasia</t>
-  </si>
-  <si>
     <t>Embla</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>Cutler</t>
   </si>
   <si>
-    <t>Emilia Trattoria</t>
-  </si>
-  <si>
     <t>Pearl Diver</t>
   </si>
   <si>
@@ -182,9 +176,6 @@
     <t>Vietnamese</t>
   </si>
   <si>
-    <t>Walrus</t>
-  </si>
-  <si>
     <t>Phillipino Fusion</t>
   </si>
   <si>
@@ -203,9 +194,6 @@
     <t>Amaru</t>
   </si>
   <si>
-    <t>Hello</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -230,7 +218,130 @@
     <t>Calc Rating</t>
   </si>
   <si>
-    <t>Type of Cuisine</t>
+    <t>https://maps.app.goo.gl/goNK3cT5DGCQLeJx9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/y8ps36MC6M1FLVQB8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RTJKMhX679KiGFWM6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GKktrSmb7xz6ZVY56</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/YdmCVSdrFZyAV87E8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/LgDaPQRKXA3YtdPZA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2T9hTCovxEqLUP3n6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/dkDv38XGsvyqyuD67</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/m9SNYH6bkYiEbHDDA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vyXvTi8mXJhA2pji9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/jZumGWz4mUnjHt2N8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/sqizgLXTTNf7xPrw9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/DUUwdVRRn8Yp8oDN8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/6ZRhWSnxqwC39p9N7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/a7mZmTwbrExYfUEi6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vvUr5sJxLtsX533x8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/AUsDQfXXZ4MaCzev7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/tNeFVUPnGVJWWdSn8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nT7G1toUtpZt84J56</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/UJAqzEon8Q9yecV88</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3e3T76W9n4YqgenG9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/gsFShWJYbq7RvUKK9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/C7PCntWqwNbfbej19</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BTCbPn4fnEYPMtQB9</t>
+  </si>
+  <si>
+    <t>The Walrus</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kkMb9c1HZUAjxMBz5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Jn59tJWgC9dMXooD6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rB6L5Twrevu1MzAU6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/4FeZLSv4LMNt9MaQ8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/sMKeoR8KdsJbdrjB7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/QtDJbqhEDeotcaN77</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/WKG9LKfed5bNknXaA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7Vo6ggQnszavkcSK6</t>
+  </si>
+  <si>
+    <t>Trattoria Emilia</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/91Ss4oHnkC5etsMVA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/dXDSmLfufyqztqDM6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/sZ35hszppUiUTdez9</t>
+  </si>
+  <si>
+    <t>Di Stasia Citta</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/eizx1R12PAWe9sxa8</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Style</t>
   </si>
   <si>
     <t>Kisume Chefs Table</t>
@@ -240,6 +351,120 @@
   </si>
   <si>
     <t>Cecconis</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>Exceptional, high quality sushi and attention to detail.</t>
+  </si>
+  <si>
+    <t>Unique Chef's table dining experience with incredible sushi</t>
+  </si>
+  <si>
+    <t>High end fine dining without the "notions"</t>
+  </si>
+  <si>
+    <t>Really trendy/tasty indian for very reasonable price</t>
+  </si>
+  <si>
+    <t>Melbourne staple, one of the best meals we've had.</t>
+  </si>
+  <si>
+    <t>High quality Japanese with great service</t>
+  </si>
+  <si>
+    <t>Absolutely delicious Italian with clever sharing setup.</t>
+  </si>
+  <si>
+    <t>Busy Portugeuse restaurant, great wine</t>
+  </si>
+  <si>
+    <t>Super tasty, super trendy Asian fusion.</t>
+  </si>
+  <si>
+    <t>High End fine dining. Multi-course menu 4+ hours. All delicious</t>
+  </si>
+  <si>
+    <t>Not strictly speaking Filipino food I'm told but very tasty/different all the same</t>
+  </si>
+  <si>
+    <t>Plenty of tast meat and sushi. Very cool décor</t>
+  </si>
+  <si>
+    <t>Lots of tasty, spicy deliciousness</t>
+  </si>
+  <si>
+    <t>Busy french wine bar is trendy neighbourhood</t>
+  </si>
+  <si>
+    <t>Super trendy wine bar. Great steak</t>
+  </si>
+  <si>
+    <t>Another Melbourne staple, busy but delicous</t>
+  </si>
+  <si>
+    <t>Trendy contemporary Australian, good for groups</t>
+  </si>
+  <si>
+    <t>Busy Middle-Eastern restaurat, multiple courses, great bread</t>
+  </si>
+  <si>
+    <t>Went for a wine event but food was also delicious</t>
+  </si>
+  <si>
+    <t>Bustling latin american joint, decent sized set menus</t>
+  </si>
+  <si>
+    <t>Random Vietnamese/French restaurant, long wait for food but everything super tasty</t>
+  </si>
+  <si>
+    <t>Stumbled across this super tasty, slighlty fancier mexican place.</t>
+  </si>
+  <si>
+    <t>Nice wine bar  near St Kilda, nice place for a drink prior to a concert in the Palais</t>
+  </si>
+  <si>
+    <t>They do a really good steak frites</t>
+  </si>
+  <si>
+    <t>Another local of ours, decent food if you can get a table outside. Great wine</t>
+  </si>
+  <si>
+    <t>Super trendy Mexican on Hosier lane</t>
+  </si>
+  <si>
+    <t>No cutlery type food, Incredibly cheap, favourful food.</t>
+  </si>
+  <si>
+    <t>Highly recommended but a bit of a let down. 3/4 of us got sick after</t>
+  </si>
+  <si>
+    <t>Predominantly a cocktail/oyster bar but decent set menu also</t>
+  </si>
+  <si>
+    <t>Busy old Italian joint. Solid meal, incredible steak but overpriced.</t>
+  </si>
+  <si>
+    <t>Very decent Italian, went for work dinner</t>
+  </si>
+  <si>
+    <t>Sister restaurant of Tonka, solid but nicer places nearby</t>
+  </si>
+  <si>
+    <t>Cosy Tapas bar, easy for walk in and bar seating</t>
+  </si>
+  <si>
+    <t>Decent Indian but portions were surprisingly small</t>
+  </si>
+  <si>
+    <t>Overpriced Italian restaurant, nothing special</t>
+  </si>
+  <si>
+    <t>One of our favourites, amazing steak. Great with friends</t>
+  </si>
+  <si>
+    <t>Our local wine bar, newly opened. Still relatively cheap, cosy French bistro upstairs</t>
   </si>
 </sst>
 </file>
@@ -616,143 +841,182 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFE0398-5E3D-42F9-829F-76BDA5454F49}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.19921875" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="4" width="12.9296875" customWidth="1"/>
-    <col min="5" max="5" width="11.59765625" customWidth="1"/>
-    <col min="6" max="6" width="13.265625" customWidth="1"/>
-    <col min="7" max="7" width="13.9296875" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.9296875" customWidth="1"/>
+    <col min="1" max="1" width="15.19921875" customWidth="1"/>
+    <col min="2" max="2" width="6.19921875" customWidth="1"/>
+    <col min="3" max="3" width="12.9296875" customWidth="1"/>
+    <col min="4" max="4" width="66.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.9296875" customWidth="1"/>
+    <col min="6" max="6" width="17.265625" customWidth="1"/>
+    <col min="7" max="7" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.59765625" customWidth="1"/>
+    <col min="9" max="9" width="10.06640625" customWidth="1"/>
+    <col min="10" max="10" width="13.9296875" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" t="s">
+      <c r="J1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1">
+        <f t="shared" ref="B2:B38" si="0">ROUND(L2,0)</f>
+        <v>94</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2">
+        <v>-37.819744399999998</v>
+      </c>
+      <c r="F2">
+        <v>145.00502520000001</v>
+      </c>
+      <c r="G2" t="s">
         <v>60</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2">
+        <v>98</v>
+      </c>
+      <c r="J2">
+        <v>98</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1">
+        <f t="shared" ref="L2:L38" si="1">((((3*I2)+(2*J2))-(5*K2))/495)*100</f>
+        <v>93.939393939393938</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="1">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3">
+        <v>-37.816214700000003</v>
+      </c>
+      <c r="F3">
+        <v>144.96879939999999</v>
+      </c>
+      <c r="G3" t="s">
         <v>61</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3">
+        <v>96</v>
+      </c>
+      <c r="J3">
+        <v>98</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1">
+        <f t="shared" si="1"/>
+        <v>92.72727272727272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="1">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4">
+        <v>-37.855813300000001</v>
+      </c>
+      <c r="F4">
+        <v>145.02494609999999</v>
+      </c>
+      <c r="G4" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="1">
-        <f t="shared" ref="B2:B38" si="0">ROUND(I2,0)</f>
-        <v>94</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2">
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4">
+        <v>97</v>
+      </c>
+      <c r="J4">
         <v>98</v>
       </c>
-      <c r="G2">
-        <v>98</v>
-      </c>
-      <c r="H2">
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="I2" s="1">
-        <f t="shared" ref="I2:I38" si="1">((((3*F2)+(2*G2))-(5*H2))/495)*100</f>
-        <v>93.939393939393938</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="1">
-        <f t="shared" si="0"/>
-        <v>93</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3">
-        <v>96</v>
-      </c>
-      <c r="G3">
-        <v>98</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3" s="1">
-        <f t="shared" si="1"/>
-        <v>92.72727272727272</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>93</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4">
-        <v>97</v>
-      </c>
-      <c r="G4">
-        <v>98</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="L4" s="1">
         <f t="shared" si="1"/>
         <v>93.333333333333329</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -761,29 +1025,38 @@
         <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
+        <v>109</v>
+      </c>
+      <c r="E5">
+        <v>-37.815699100000003</v>
       </c>
       <c r="F5">
+        <v>144.97141070000001</v>
+      </c>
+      <c r="G5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5">
         <v>93</v>
       </c>
-      <c r="G5">
+      <c r="J5">
         <v>94</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>3.5</v>
       </c>
-      <c r="I5" s="1">
+      <c r="L5" s="1">
         <f t="shared" si="1"/>
         <v>90.808080808080803</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -792,29 +1065,38 @@
         <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
+        <v>141</v>
+      </c>
+      <c r="E6">
+        <v>-37.812163599999998</v>
       </c>
       <c r="F6">
+        <v>144.97241320000001</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6">
         <v>94</v>
       </c>
-      <c r="G6">
+      <c r="J6">
         <v>94</v>
       </c>
-      <c r="H6">
+      <c r="K6">
         <v>4.5</v>
       </c>
-      <c r="I6" s="1">
+      <c r="L6" s="1">
         <f t="shared" si="1"/>
         <v>90.404040404040416</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -823,29 +1105,38 @@
         <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
+        <v>110</v>
+      </c>
+      <c r="E7">
+        <v>-37.816716700000001</v>
       </c>
       <c r="F7">
+        <v>144.96914169999999</v>
+      </c>
+      <c r="G7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7">
         <v>94</v>
       </c>
-      <c r="G7">
+      <c r="J7">
         <v>90</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>4</v>
       </c>
-      <c r="I7" s="1">
+      <c r="L7" s="1">
         <f t="shared" si="1"/>
         <v>89.292929292929287</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -854,29 +1145,38 @@
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
+        <v>111</v>
+      </c>
+      <c r="E8">
+        <v>-37.816099999999999</v>
       </c>
       <c r="F8">
+        <v>144.96879939999999</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8">
         <v>95</v>
       </c>
-      <c r="G8">
+      <c r="J8">
         <v>90</v>
       </c>
-      <c r="H8">
+      <c r="K8">
         <v>4.5</v>
       </c>
-      <c r="I8" s="1">
+      <c r="L8" s="1">
         <f t="shared" si="1"/>
         <v>89.393939393939391</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -885,60 +1185,78 @@
         <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9">
+        <v>-37.814523000000001</v>
+      </c>
+      <c r="F9">
+        <v>144.974164</v>
+      </c>
+      <c r="G9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>89</v>
+      </c>
+      <c r="J9">
+        <v>90</v>
+      </c>
+      <c r="K9">
+        <v>2.5</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="1"/>
+        <v>87.777777777777771</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="F9">
-        <v>89</v>
-      </c>
-      <c r="G9">
+      <c r="D10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10">
+        <v>-37.813552199999997</v>
+      </c>
+      <c r="F10">
+        <v>144.9619835</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10">
+        <v>92</v>
+      </c>
+      <c r="J10">
         <v>90</v>
       </c>
-      <c r="H9">
-        <v>2.5</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="1"/>
-        <v>87.777777777777771</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>88</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10">
-        <v>92</v>
-      </c>
-      <c r="G10">
-        <v>90</v>
-      </c>
-      <c r="H10">
+      <c r="K10">
         <v>4</v>
       </c>
-      <c r="I10" s="1">
+      <c r="L10" s="1">
         <f t="shared" si="1"/>
         <v>88.080808080808083</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -947,60 +1265,78 @@
         <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
+        <v>113</v>
+      </c>
+      <c r="E11">
+        <v>-37.813279100000003</v>
       </c>
       <c r="F11">
+        <v>144.96851409999999</v>
+      </c>
+      <c r="G11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11">
         <v>89</v>
       </c>
-      <c r="G11">
+      <c r="J11">
         <v>92</v>
       </c>
-      <c r="H11">
+      <c r="K11">
         <v>4</v>
       </c>
-      <c r="I11" s="1">
+      <c r="L11" s="1">
         <f t="shared" si="1"/>
         <v>87.070707070707059</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>29</v>
+        <v>114</v>
+      </c>
+      <c r="E12">
+        <v>-37.815992799999997</v>
       </c>
       <c r="F12">
+        <v>144.96995380000001</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12">
         <v>89</v>
       </c>
-      <c r="G12">
+      <c r="J12">
         <v>90</v>
       </c>
-      <c r="H12">
+      <c r="K12">
         <v>3.5</v>
       </c>
-      <c r="I12" s="1">
+      <c r="L12" s="1">
         <f t="shared" si="1"/>
         <v>86.767676767676775</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -1009,60 +1345,78 @@
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>29</v>
+        <v>115</v>
+      </c>
+      <c r="E13">
+        <v>-37.8181528</v>
       </c>
       <c r="F13">
+        <v>144.96266199999999</v>
+      </c>
+      <c r="G13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13">
         <v>92</v>
       </c>
-      <c r="G13">
+      <c r="J13">
         <v>88</v>
       </c>
-      <c r="H13">
+      <c r="K13">
         <v>5</v>
       </c>
-      <c r="I13" s="1">
+      <c r="L13" s="1">
         <f t="shared" si="1"/>
         <v>86.26262626262627</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" t="s">
-        <v>29</v>
+        <v>116</v>
+      </c>
+      <c r="E14">
+        <v>-37.813893700000001</v>
       </c>
       <c r="F14">
+        <v>144.96168950000001</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14">
         <v>90</v>
       </c>
-      <c r="G14">
+      <c r="J14">
         <v>89</v>
       </c>
-      <c r="H14">
+      <c r="K14">
         <v>4</v>
       </c>
-      <c r="I14" s="1">
+      <c r="L14" s="1">
         <f t="shared" si="1"/>
         <v>86.464646464646464</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1071,29 +1425,38 @@
         <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
+        <v>117</v>
+      </c>
+      <c r="E15">
+        <v>-37.815804300000003</v>
       </c>
       <c r="F15">
+        <v>144.97253459999999</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15">
         <v>87</v>
       </c>
-      <c r="G15">
+      <c r="J15">
         <v>89</v>
       </c>
-      <c r="H15">
+      <c r="K15">
         <v>4</v>
       </c>
-      <c r="I15" s="1">
+      <c r="L15" s="1">
         <f t="shared" si="1"/>
         <v>84.646464646464651</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1102,91 +1465,118 @@
         <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" t="s">
-        <v>29</v>
+        <v>118</v>
+      </c>
+      <c r="E16">
+        <v>-37.815840299999998</v>
       </c>
       <c r="F16">
+        <v>144.9710359</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16">
         <v>89</v>
       </c>
-      <c r="G16">
+      <c r="J16">
         <v>85</v>
       </c>
-      <c r="H16">
+      <c r="K16">
         <v>3.5</v>
       </c>
-      <c r="I16" s="1">
+      <c r="L16" s="1">
         <f t="shared" si="1"/>
         <v>84.747474747474755</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" t="s">
-        <v>29</v>
+        <v>119</v>
+      </c>
+      <c r="E17">
+        <v>-37.805473399999997</v>
       </c>
       <c r="F17">
+        <v>144.97585419999999</v>
+      </c>
+      <c r="G17" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17">
         <v>89</v>
       </c>
-      <c r="G17">
+      <c r="J17">
         <v>87</v>
       </c>
-      <c r="H17">
+      <c r="K17">
         <v>4</v>
       </c>
-      <c r="I17" s="1">
+      <c r="L17" s="1">
         <f t="shared" si="1"/>
         <v>85.050505050505052</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" t="s">
-        <v>29</v>
+        <v>120</v>
+      </c>
+      <c r="E18">
+        <v>-37.813394000000002</v>
       </c>
       <c r="F18">
+        <v>144.9686092</v>
+      </c>
+      <c r="G18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18">
         <v>90</v>
       </c>
-      <c r="G18">
+      <c r="J18">
         <v>86</v>
       </c>
-      <c r="H18">
+      <c r="K18">
         <v>4</v>
       </c>
-      <c r="I18" s="1">
+      <c r="L18" s="1">
         <f t="shared" si="1"/>
         <v>85.25252525252526</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1195,29 +1585,38 @@
         <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" t="s">
-        <v>29</v>
+        <v>121</v>
+      </c>
+      <c r="E19">
+        <v>-37.814913199999999</v>
       </c>
       <c r="F19">
+        <v>144.97312289999999</v>
+      </c>
+      <c r="G19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19">
         <v>90</v>
       </c>
-      <c r="G19">
+      <c r="J19">
         <v>85</v>
       </c>
-      <c r="H19">
+      <c r="K19">
         <v>3.5</v>
       </c>
-      <c r="I19" s="1">
+      <c r="L19" s="1">
         <f t="shared" si="1"/>
         <v>85.353535353535349</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1226,29 +1625,38 @@
         <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" t="s">
-        <v>29</v>
+        <v>122</v>
+      </c>
+      <c r="E20">
+        <v>-37.815887199999999</v>
       </c>
       <c r="F20">
+        <v>144.96873160000001</v>
+      </c>
+      <c r="G20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20">
         <v>86</v>
       </c>
-      <c r="G20">
+      <c r="J20">
         <v>89</v>
       </c>
-      <c r="H20">
+      <c r="K20">
         <v>4</v>
       </c>
-      <c r="I20" s="1">
+      <c r="L20" s="1">
         <f t="shared" si="1"/>
         <v>84.040404040404042</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1257,122 +1665,158 @@
         <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" t="s">
-        <v>29</v>
+        <v>123</v>
+      </c>
+      <c r="E21">
+        <v>-37.816189100000003</v>
       </c>
       <c r="F21">
+        <v>144.9683115</v>
+      </c>
+      <c r="G21" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21">
         <v>87</v>
       </c>
-      <c r="G21">
+      <c r="J21">
         <v>88</v>
       </c>
-      <c r="H21">
+      <c r="K21">
         <v>4</v>
       </c>
-      <c r="I21" s="1">
+      <c r="L21" s="1">
         <f t="shared" si="1"/>
         <v>84.242424242424235</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" t="s">
-        <v>29</v>
+        <v>124</v>
+      </c>
+      <c r="E22">
+        <v>-37.805464999999998</v>
       </c>
       <c r="F22">
+        <v>144.97589930000001</v>
+      </c>
+      <c r="G22" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22">
         <v>87</v>
       </c>
-      <c r="G22">
+      <c r="J22">
         <v>87</v>
       </c>
-      <c r="H22">
+      <c r="K22">
         <v>3.5</v>
       </c>
-      <c r="I22" s="1">
+      <c r="L22" s="1">
         <f t="shared" si="1"/>
         <v>84.343434343434339</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="C23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23">
+        <v>-37.8063845</v>
+      </c>
+      <c r="F23">
+        <v>144.98510970000001</v>
+      </c>
+      <c r="G23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23">
+        <v>84</v>
+      </c>
+      <c r="J23">
+        <v>88</v>
+      </c>
+      <c r="K23">
+        <v>3.5</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="1"/>
+        <v>82.929292929292927</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="1">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
         <v>45</v>
       </c>
-      <c r="D23" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23">
-        <v>84</v>
-      </c>
-      <c r="G23">
-        <v>88</v>
-      </c>
-      <c r="H23">
+      <c r="D24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24">
+        <v>-37.795028600000002</v>
+      </c>
+      <c r="F24">
+        <v>144.9792506</v>
+      </c>
+      <c r="G24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24">
+        <v>90</v>
+      </c>
+      <c r="J24">
+        <v>80</v>
+      </c>
+      <c r="K24">
         <v>3.5</v>
       </c>
-      <c r="I23" s="1">
-        <f t="shared" si="1"/>
-        <v>82.929292929292927</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24">
-        <v>90</v>
-      </c>
-      <c r="G24">
-        <v>80</v>
-      </c>
-      <c r="H24">
-        <v>3.5</v>
-      </c>
-      <c r="I24" s="1">
+      <c r="L24" s="1">
         <f t="shared" si="1"/>
         <v>83.333333333333343</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1381,122 +1825,158 @@
         <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" t="s">
-        <v>29</v>
+        <v>127</v>
+      </c>
+      <c r="E25">
+        <v>-37.8136394</v>
       </c>
       <c r="F25">
+        <v>144.9733909</v>
+      </c>
+      <c r="G25" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25">
         <v>85</v>
       </c>
-      <c r="G25">
+      <c r="J25">
         <v>85</v>
       </c>
-      <c r="H25">
+      <c r="K25">
         <v>3.5</v>
       </c>
-      <c r="I25" s="1">
+      <c r="L25" s="1">
         <f t="shared" si="1"/>
         <v>82.323232323232318</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" t="s">
-        <v>29</v>
+        <v>128</v>
+      </c>
+      <c r="E26">
+        <v>-37.864322399999999</v>
       </c>
       <c r="F26">
+        <v>144.98226339999999</v>
+      </c>
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26">
         <v>84</v>
       </c>
-      <c r="G26">
+      <c r="J26">
         <v>84</v>
       </c>
-      <c r="H26">
+      <c r="K26">
         <v>2.5</v>
       </c>
-      <c r="I26" s="1">
+      <c r="L26" s="1">
         <f t="shared" si="1"/>
         <v>82.323232323232318</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" t="s">
-        <v>29</v>
+        <v>129</v>
+      </c>
+      <c r="E27">
+        <v>-37.849426999999999</v>
       </c>
       <c r="F27">
+        <v>144.99151900000001</v>
+      </c>
+      <c r="G27" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27">
         <v>80</v>
       </c>
-      <c r="G27">
+      <c r="J27">
         <v>88</v>
       </c>
-      <c r="H27">
+      <c r="K27">
         <v>3.5</v>
       </c>
-      <c r="I27" s="1">
+      <c r="L27" s="1">
         <f t="shared" si="1"/>
         <v>80.505050505050505</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" t="s">
-        <v>29</v>
+        <v>130</v>
+      </c>
+      <c r="E28">
+        <v>-37.810980200000003</v>
       </c>
       <c r="F28">
+        <v>144.97253789999999</v>
+      </c>
+      <c r="G28" t="s">
         <v>86</v>
       </c>
-      <c r="G28">
+      <c r="H28" t="s">
+        <v>27</v>
+      </c>
+      <c r="I28">
+        <v>86</v>
+      </c>
+      <c r="J28">
         <v>78</v>
       </c>
-      <c r="H28">
+      <c r="K28">
         <v>3</v>
       </c>
-      <c r="I28" s="1">
+      <c r="L28" s="1">
         <f t="shared" si="1"/>
         <v>80.606060606060609</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1505,309 +1985,399 @@
         <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29">
+        <v>-37.816451299999997</v>
+      </c>
+      <c r="F29">
+        <v>144.96909969999999</v>
+      </c>
+      <c r="G29" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I29">
+        <v>83</v>
+      </c>
+      <c r="J29">
+        <v>85</v>
+      </c>
+      <c r="K29">
+        <v>3.5</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" si="1"/>
+        <v>81.111111111111114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="1">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30">
+        <v>-37.788539800000002</v>
+      </c>
+      <c r="F30">
+        <v>144.9318371</v>
+      </c>
+      <c r="G30" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" t="s">
+        <v>27</v>
+      </c>
+      <c r="I30">
+        <v>84</v>
+      </c>
+      <c r="J30">
+        <v>80</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="1"/>
+        <v>81.212121212121218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="1">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31">
+        <v>-37.813554099999998</v>
+      </c>
+      <c r="F31">
+        <v>144.97102520000001</v>
+      </c>
+      <c r="G31" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31">
+        <v>87</v>
+      </c>
+      <c r="J31">
+        <v>80</v>
+      </c>
+      <c r="K31">
+        <v>5</v>
+      </c>
+      <c r="L31" s="1">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="1">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32">
+        <v>-37.810779599999996</v>
+      </c>
+      <c r="F32">
+        <v>144.97079550000001</v>
+      </c>
+      <c r="G32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H32" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32">
+        <v>80</v>
+      </c>
+      <c r="J32">
+        <v>82</v>
+      </c>
+      <c r="K32">
+        <v>3</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" si="1"/>
+        <v>78.585858585858574</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="1">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="C33" t="s">
         <v>29</v>
       </c>
-      <c r="F29">
-        <v>83</v>
-      </c>
-      <c r="G29">
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33">
+        <v>-37.8150555</v>
+      </c>
+      <c r="F33">
+        <v>144.97252929999999</v>
+      </c>
+      <c r="G33" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33">
         <v>85</v>
       </c>
-      <c r="H29">
+      <c r="J33">
+        <v>78</v>
+      </c>
+      <c r="K33">
+        <v>4</v>
+      </c>
+      <c r="L33" s="1">
+        <f t="shared" si="1"/>
+        <v>78.98989898989899</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="1">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="C34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34">
+        <v>-37.815333000000003</v>
+      </c>
+      <c r="F34">
+        <v>144.96267309999999</v>
+      </c>
+      <c r="G34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34">
+        <v>80</v>
+      </c>
+      <c r="J34">
+        <v>84</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34" s="1">
+        <f t="shared" si="1"/>
+        <v>78.383838383838395</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="1">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35">
+        <v>-37.815766099999998</v>
+      </c>
+      <c r="F35">
+        <v>144.96988970000001</v>
+      </c>
+      <c r="G35" t="s">
+        <v>94</v>
+      </c>
+      <c r="H35" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35">
+        <v>82</v>
+      </c>
+      <c r="J35">
+        <v>74</v>
+      </c>
+      <c r="K35">
         <v>3.5</v>
       </c>
-      <c r="I29" s="1">
-        <f t="shared" si="1"/>
-        <v>81.111111111111114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="L35" s="1">
+        <f t="shared" si="1"/>
+        <v>76.060606060606062</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" s="1">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36">
+        <v>-37.812815000000001</v>
+      </c>
+      <c r="F36">
+        <v>144.97251850000001</v>
+      </c>
+      <c r="G36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36">
+        <v>72</v>
+      </c>
+      <c r="J36">
+        <v>82</v>
+      </c>
+      <c r="K36">
+        <v>2.5</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" si="1"/>
+        <v>74.242424242424249</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="1">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37">
+        <v>-37.815731999999997</v>
+      </c>
+      <c r="F37">
+        <v>144.97268800000001</v>
+      </c>
+      <c r="G37" t="s">
+        <v>96</v>
+      </c>
+      <c r="H37" t="s">
+        <v>27</v>
+      </c>
+      <c r="I37">
+        <v>75</v>
+      </c>
+      <c r="J37">
+        <v>70</v>
+      </c>
+      <c r="K37">
+        <v>3</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="1"/>
+        <v>70.707070707070713</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="1">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C38" t="s">
         <v>29</v>
       </c>
-      <c r="F30">
-        <v>84</v>
-      </c>
-      <c r="G30">
-        <v>80</v>
-      </c>
-      <c r="H30">
-        <v>2</v>
-      </c>
-      <c r="I30" s="1">
-        <f t="shared" si="1"/>
-        <v>81.212121212121218</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31">
-        <v>87</v>
-      </c>
-      <c r="G31">
-        <v>80</v>
-      </c>
-      <c r="H31">
-        <v>5</v>
-      </c>
-      <c r="I31" s="1">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="1">
-        <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-      <c r="C32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32">
-        <v>80</v>
-      </c>
-      <c r="G32">
-        <v>82</v>
-      </c>
-      <c r="H32">
-        <v>3</v>
-      </c>
-      <c r="I32" s="1">
-        <f t="shared" si="1"/>
-        <v>78.585858585858574</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="1">
-        <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-      <c r="C33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" t="s">
-        <v>55</v>
-      </c>
-      <c r="E33" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33">
-        <v>85</v>
-      </c>
-      <c r="G33">
-        <v>78</v>
-      </c>
-      <c r="H33">
-        <v>4</v>
-      </c>
-      <c r="I33" s="1">
-        <f t="shared" si="1"/>
-        <v>78.98989898989899</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="1">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
-      <c r="C34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34">
-        <v>80</v>
-      </c>
-      <c r="G34">
-        <v>84</v>
-      </c>
-      <c r="H34">
-        <v>4</v>
-      </c>
-      <c r="I34" s="1">
-        <f t="shared" si="1"/>
-        <v>78.383838383838395</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="1">
-        <f t="shared" si="0"/>
-        <v>76</v>
-      </c>
-      <c r="C35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" t="s">
-        <v>29</v>
-      </c>
-      <c r="F35">
-        <v>82</v>
-      </c>
-      <c r="G35">
-        <v>74</v>
-      </c>
-      <c r="H35">
-        <v>3.5</v>
-      </c>
-      <c r="I35" s="1">
-        <f t="shared" si="1"/>
-        <v>76.060606060606062</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="1">
-        <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36">
-        <v>72</v>
-      </c>
-      <c r="G36">
-        <v>82</v>
-      </c>
-      <c r="H36">
-        <v>2.5</v>
-      </c>
-      <c r="I36" s="1">
-        <f t="shared" si="1"/>
-        <v>74.242424242424249</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="1">
-        <f t="shared" si="0"/>
-        <v>71</v>
-      </c>
-      <c r="C37" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37">
-        <v>75</v>
-      </c>
-      <c r="G37">
+      <c r="D38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38">
+        <v>-37.814254800000001</v>
+      </c>
+      <c r="F38">
+        <v>144.974186</v>
+      </c>
+      <c r="G38" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38">
         <v>70</v>
       </c>
-      <c r="H37">
-        <v>3</v>
-      </c>
-      <c r="I37" s="1">
-        <f t="shared" si="1"/>
-        <v>70.707070707070713</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="1">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="C38" t="s">
-        <v>31</v>
-      </c>
-      <c r="D38" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38">
-        <v>70</v>
-      </c>
-      <c r="G38">
+      <c r="J38">
         <v>60</v>
       </c>
-      <c r="H38">
+      <c r="K38">
         <v>4.5</v>
       </c>
-      <c r="I38" s="1">
+      <c r="L38" s="1">
         <f t="shared" si="1"/>
         <v>62.121212121212125</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I38">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L38">
     <sortCondition descending="1" ref="B2:B38"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats - Copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF0EFF22-B412-4861-B0D6-67EC963AD0E0}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACDDF452-2E1F-4BF6-A069-2A3139F54BD1}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -518,10 +518,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -852,9 +848,9 @@
     <col min="6" max="6" width="17.265625" customWidth="1"/>
     <col min="7" max="7" width="10.796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.59765625" customWidth="1"/>
-    <col min="9" max="9" width="10.06640625" customWidth="1"/>
-    <col min="10" max="10" width="13.9296875" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.06640625" customWidth="1"/>
+    <col min="11" max="11" width="13.9296875" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -884,13 +880,13 @@
         <v>55</v>
       </c>
       <c r="I1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" t="s">
         <v>56</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>57</v>
-      </c>
-      <c r="K1" t="s">
-        <v>58</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>59</v>
@@ -923,16 +919,16 @@
         <v>27</v>
       </c>
       <c r="I2">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>98</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="L2" s="1">
-        <f t="shared" ref="L2:L38" si="1">((((3*I2)+(2*J2))-(5*K2))/495)*100</f>
+        <f>((((3*J2)+(2*K2))-(5*I2))/495)*100</f>
         <v>93.939393939393938</v>
       </c>
     </row>
@@ -963,16 +959,16 @@
         <v>27</v>
       </c>
       <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
         <v>96</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>98</v>
       </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
       <c r="L3" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J3)+(2*K3))-(5*I3))/495)*100</f>
         <v>92.72727272727272</v>
       </c>
     </row>
@@ -1003,16 +999,16 @@
         <v>27</v>
       </c>
       <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <v>97</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>98</v>
       </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
       <c r="L4" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J4)+(2*K4))-(5*I4))/495)*100</f>
         <v>93.333333333333329</v>
       </c>
     </row>
@@ -1043,16 +1039,16 @@
         <v>27</v>
       </c>
       <c r="I5">
+        <v>3.5</v>
+      </c>
+      <c r="J5">
         <v>93</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>94</v>
       </c>
-      <c r="K5">
-        <v>3.5</v>
-      </c>
       <c r="L5" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J5)+(2*K5))-(5*I5))/495)*100</f>
         <v>90.808080808080803</v>
       </c>
     </row>
@@ -1083,16 +1079,16 @@
         <v>27</v>
       </c>
       <c r="I6">
-        <v>94</v>
+        <v>4.5</v>
       </c>
       <c r="J6">
         <v>94</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>94</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J6)+(2*K6))-(5*I6))/495)*100</f>
         <v>90.404040404040416</v>
       </c>
     </row>
@@ -1123,16 +1119,16 @@
         <v>27</v>
       </c>
       <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
         <v>94</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>90</v>
       </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
       <c r="L7" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J7)+(2*K7))-(5*I7))/495)*100</f>
         <v>89.292929292929287</v>
       </c>
     </row>
@@ -1163,16 +1159,16 @@
         <v>27</v>
       </c>
       <c r="I8">
+        <v>4.5</v>
+      </c>
+      <c r="J8">
         <v>95</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>90</v>
       </c>
-      <c r="K8">
-        <v>4.5</v>
-      </c>
       <c r="L8" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J8)+(2*K8))-(5*I8))/495)*100</f>
         <v>89.393939393939391</v>
       </c>
     </row>
@@ -1203,16 +1199,16 @@
         <v>27</v>
       </c>
       <c r="I9">
+        <v>2.5</v>
+      </c>
+      <c r="J9">
         <v>89</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>90</v>
       </c>
-      <c r="K9">
-        <v>2.5</v>
-      </c>
       <c r="L9" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J9)+(2*K9))-(5*I9))/495)*100</f>
         <v>87.777777777777771</v>
       </c>
     </row>
@@ -1243,16 +1239,16 @@
         <v>27</v>
       </c>
       <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
         <v>92</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>90</v>
       </c>
-      <c r="K10">
-        <v>4</v>
-      </c>
       <c r="L10" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J10)+(2*K10))-(5*I10))/495)*100</f>
         <v>88.080808080808083</v>
       </c>
     </row>
@@ -1283,16 +1279,16 @@
         <v>27</v>
       </c>
       <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
         <v>89</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>92</v>
       </c>
-      <c r="K11">
-        <v>4</v>
-      </c>
       <c r="L11" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J11)+(2*K11))-(5*I11))/495)*100</f>
         <v>87.070707070707059</v>
       </c>
     </row>
@@ -1323,16 +1319,16 @@
         <v>27</v>
       </c>
       <c r="I12">
+        <v>3.5</v>
+      </c>
+      <c r="J12">
         <v>89</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>90</v>
       </c>
-      <c r="K12">
-        <v>3.5</v>
-      </c>
       <c r="L12" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J12)+(2*K12))-(5*I12))/495)*100</f>
         <v>86.767676767676775</v>
       </c>
     </row>
@@ -1363,16 +1359,16 @@
         <v>27</v>
       </c>
       <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
         <v>92</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>88</v>
       </c>
-      <c r="K13">
-        <v>5</v>
-      </c>
       <c r="L13" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J13)+(2*K13))-(5*I13))/495)*100</f>
         <v>86.26262626262627</v>
       </c>
     </row>
@@ -1403,16 +1399,16 @@
         <v>27</v>
       </c>
       <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14">
         <v>90</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>89</v>
       </c>
-      <c r="K14">
-        <v>4</v>
-      </c>
       <c r="L14" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J14)+(2*K14))-(5*I14))/495)*100</f>
         <v>86.464646464646464</v>
       </c>
     </row>
@@ -1443,16 +1439,16 @@
         <v>27</v>
       </c>
       <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15">
         <v>87</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>89</v>
       </c>
-      <c r="K15">
-        <v>4</v>
-      </c>
       <c r="L15" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J15)+(2*K15))-(5*I15))/495)*100</f>
         <v>84.646464646464651</v>
       </c>
     </row>
@@ -1483,16 +1479,16 @@
         <v>27</v>
       </c>
       <c r="I16">
+        <v>3.5</v>
+      </c>
+      <c r="J16">
         <v>89</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>85</v>
       </c>
-      <c r="K16">
-        <v>3.5</v>
-      </c>
       <c r="L16" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J16)+(2*K16))-(5*I16))/495)*100</f>
         <v>84.747474747474755</v>
       </c>
     </row>
@@ -1523,16 +1519,16 @@
         <v>27</v>
       </c>
       <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17">
         <v>89</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>87</v>
       </c>
-      <c r="K17">
-        <v>4</v>
-      </c>
       <c r="L17" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J17)+(2*K17))-(5*I17))/495)*100</f>
         <v>85.050505050505052</v>
       </c>
     </row>
@@ -1563,16 +1559,16 @@
         <v>27</v>
       </c>
       <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="J18">
         <v>90</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>86</v>
       </c>
-      <c r="K18">
-        <v>4</v>
-      </c>
       <c r="L18" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J18)+(2*K18))-(5*I18))/495)*100</f>
         <v>85.25252525252526</v>
       </c>
     </row>
@@ -1603,16 +1599,16 @@
         <v>27</v>
       </c>
       <c r="I19">
+        <v>3.5</v>
+      </c>
+      <c r="J19">
         <v>90</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>85</v>
       </c>
-      <c r="K19">
-        <v>3.5</v>
-      </c>
       <c r="L19" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J19)+(2*K19))-(5*I19))/495)*100</f>
         <v>85.353535353535349</v>
       </c>
     </row>
@@ -1643,16 +1639,16 @@
         <v>27</v>
       </c>
       <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20">
         <v>86</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>89</v>
       </c>
-      <c r="K20">
-        <v>4</v>
-      </c>
       <c r="L20" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J20)+(2*K20))-(5*I20))/495)*100</f>
         <v>84.040404040404042</v>
       </c>
     </row>
@@ -1683,16 +1679,16 @@
         <v>27</v>
       </c>
       <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="J21">
         <v>87</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>88</v>
       </c>
-      <c r="K21">
-        <v>4</v>
-      </c>
       <c r="L21" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J21)+(2*K21))-(5*I21))/495)*100</f>
         <v>84.242424242424235</v>
       </c>
     </row>
@@ -1723,16 +1719,16 @@
         <v>27</v>
       </c>
       <c r="I22">
-        <v>87</v>
+        <v>3.5</v>
       </c>
       <c r="J22">
         <v>87</v>
       </c>
       <c r="K22">
-        <v>3.5</v>
+        <v>87</v>
       </c>
       <c r="L22" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J22)+(2*K22))-(5*I22))/495)*100</f>
         <v>84.343434343434339</v>
       </c>
     </row>
@@ -1763,16 +1759,16 @@
         <v>27</v>
       </c>
       <c r="I23">
+        <v>3.5</v>
+      </c>
+      <c r="J23">
         <v>84</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>88</v>
       </c>
-      <c r="K23">
-        <v>3.5</v>
-      </c>
       <c r="L23" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J23)+(2*K23))-(5*I23))/495)*100</f>
         <v>82.929292929292927</v>
       </c>
     </row>
@@ -1803,16 +1799,16 @@
         <v>27</v>
       </c>
       <c r="I24">
+        <v>3.5</v>
+      </c>
+      <c r="J24">
         <v>90</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>80</v>
       </c>
-      <c r="K24">
-        <v>3.5</v>
-      </c>
       <c r="L24" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J24)+(2*K24))-(5*I24))/495)*100</f>
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -1843,16 +1839,16 @@
         <v>27</v>
       </c>
       <c r="I25">
-        <v>85</v>
+        <v>3.5</v>
       </c>
       <c r="J25">
         <v>85</v>
       </c>
       <c r="K25">
-        <v>3.5</v>
+        <v>85</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J25)+(2*K25))-(5*I25))/495)*100</f>
         <v>82.323232323232318</v>
       </c>
     </row>
@@ -1883,16 +1879,16 @@
         <v>27</v>
       </c>
       <c r="I26">
-        <v>84</v>
+        <v>2.5</v>
       </c>
       <c r="J26">
         <v>84</v>
       </c>
       <c r="K26">
-        <v>2.5</v>
+        <v>84</v>
       </c>
       <c r="L26" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J26)+(2*K26))-(5*I26))/495)*100</f>
         <v>82.323232323232318</v>
       </c>
     </row>
@@ -1923,16 +1919,16 @@
         <v>27</v>
       </c>
       <c r="I27">
+        <v>3.5</v>
+      </c>
+      <c r="J27">
         <v>80</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>88</v>
       </c>
-      <c r="K27">
-        <v>3.5</v>
-      </c>
       <c r="L27" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J27)+(2*K27))-(5*I27))/495)*100</f>
         <v>80.505050505050505</v>
       </c>
     </row>
@@ -1963,16 +1959,16 @@
         <v>27</v>
       </c>
       <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28">
         <v>86</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>78</v>
       </c>
-      <c r="K28">
-        <v>3</v>
-      </c>
       <c r="L28" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J28)+(2*K28))-(5*I28))/495)*100</f>
         <v>80.606060606060609</v>
       </c>
     </row>
@@ -2003,16 +1999,16 @@
         <v>27</v>
       </c>
       <c r="I29">
+        <v>3.5</v>
+      </c>
+      <c r="J29">
         <v>83</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>85</v>
       </c>
-      <c r="K29">
-        <v>3.5</v>
-      </c>
       <c r="L29" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J29)+(2*K29))-(5*I29))/495)*100</f>
         <v>81.111111111111114</v>
       </c>
     </row>
@@ -2043,16 +2039,16 @@
         <v>27</v>
       </c>
       <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
         <v>84</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>80</v>
       </c>
-      <c r="K30">
-        <v>2</v>
-      </c>
       <c r="L30" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J30)+(2*K30))-(5*I30))/495)*100</f>
         <v>81.212121212121218</v>
       </c>
     </row>
@@ -2083,16 +2079,16 @@
         <v>27</v>
       </c>
       <c r="I31">
+        <v>5</v>
+      </c>
+      <c r="J31">
         <v>87</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>80</v>
       </c>
-      <c r="K31">
-        <v>5</v>
-      </c>
       <c r="L31" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J31)+(2*K31))-(5*I31))/495)*100</f>
         <v>80</v>
       </c>
     </row>
@@ -2123,16 +2119,16 @@
         <v>27</v>
       </c>
       <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
         <v>80</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>82</v>
       </c>
-      <c r="K32">
-        <v>3</v>
-      </c>
       <c r="L32" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J32)+(2*K32))-(5*I32))/495)*100</f>
         <v>78.585858585858574</v>
       </c>
     </row>
@@ -2163,16 +2159,16 @@
         <v>27</v>
       </c>
       <c r="I33">
+        <v>4</v>
+      </c>
+      <c r="J33">
         <v>85</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>78</v>
       </c>
-      <c r="K33">
-        <v>4</v>
-      </c>
       <c r="L33" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J33)+(2*K33))-(5*I33))/495)*100</f>
         <v>78.98989898989899</v>
       </c>
     </row>
@@ -2203,16 +2199,16 @@
         <v>27</v>
       </c>
       <c r="I34">
+        <v>4</v>
+      </c>
+      <c r="J34">
         <v>80</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>84</v>
       </c>
-      <c r="K34">
-        <v>4</v>
-      </c>
       <c r="L34" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J34)+(2*K34))-(5*I34))/495)*100</f>
         <v>78.383838383838395</v>
       </c>
     </row>
@@ -2243,16 +2239,16 @@
         <v>27</v>
       </c>
       <c r="I35">
+        <v>3.5</v>
+      </c>
+      <c r="J35">
         <v>82</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>74</v>
       </c>
-      <c r="K35">
-        <v>3.5</v>
-      </c>
       <c r="L35" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J35)+(2*K35))-(5*I35))/495)*100</f>
         <v>76.060606060606062</v>
       </c>
     </row>
@@ -2283,16 +2279,16 @@
         <v>27</v>
       </c>
       <c r="I36">
+        <v>2.5</v>
+      </c>
+      <c r="J36">
         <v>72</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>82</v>
       </c>
-      <c r="K36">
-        <v>2.5</v>
-      </c>
       <c r="L36" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J36)+(2*K36))-(5*I36))/495)*100</f>
         <v>74.242424242424249</v>
       </c>
     </row>
@@ -2323,16 +2319,16 @@
         <v>27</v>
       </c>
       <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37">
         <v>75</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>70</v>
       </c>
-      <c r="K37">
-        <v>3</v>
-      </c>
       <c r="L37" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J37)+(2*K37))-(5*I37))/495)*100</f>
         <v>70.707070707070713</v>
       </c>
     </row>
@@ -2363,16 +2359,16 @@
         <v>27</v>
       </c>
       <c r="I38">
+        <v>4.5</v>
+      </c>
+      <c r="J38">
         <v>70</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>60</v>
       </c>
-      <c r="K38">
-        <v>4.5</v>
-      </c>
       <c r="L38" s="1">
-        <f t="shared" si="1"/>
+        <f>((((3*J38)+(2*K38))-(5*I38))/495)*100</f>
         <v>62.121212121212125</v>
       </c>
     </row>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats - Copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACDDF452-2E1F-4BF6-A069-2A3139F54BD1}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED9DB3C8-DAE7-49AC-81DC-71A0B5FFEA17}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="150">
   <si>
     <t>San Telmo</t>
   </si>
@@ -465,6 +465,27 @@
   </si>
   <si>
     <t>Our local wine bar, newly opened. Still relatively cheap, cosy French bistro upstairs</t>
+  </si>
+  <si>
+    <t>Cocktail</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Australian</t>
+  </si>
+  <si>
+    <t>Central/South American</t>
+  </si>
+  <si>
+    <t>European</t>
+  </si>
+  <si>
+    <t>Middle East/Africa</t>
   </si>
 </sst>
 </file>
@@ -837,24 +858,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFE0398-5E3D-42F9-829F-76BDA5454F49}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.19921875" customWidth="1"/>
-    <col min="2" max="2" width="6.19921875" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" customWidth="1"/>
     <col min="3" max="3" width="12.9296875" customWidth="1"/>
-    <col min="4" max="4" width="66.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.9296875" customWidth="1"/>
-    <col min="6" max="6" width="17.265625" customWidth="1"/>
-    <col min="7" max="7" width="10.796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.59765625" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="10.06640625" customWidth="1"/>
-    <col min="11" max="11" width="13.9296875" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.19921875" customWidth="1"/>
+    <col min="5" max="5" width="66.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.9296875" customWidth="1"/>
+    <col min="7" max="7" width="17.265625" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="10.06640625" customWidth="1"/>
+    <col min="12" max="12" width="13.9296875" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -865,74 +887,80 @@
         <v>101</v>
       </c>
       <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
         <v>54</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>100</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>99</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>105</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>55</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>58</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>56</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>57</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2" s="1">
-        <f t="shared" ref="B2:B38" si="0">ROUND(L2,0)</f>
+        <f t="shared" ref="B2:B38" si="0">ROUND(M2,0)</f>
         <v>94</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
       </c>
       <c r="D2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" t="s">
         <v>106</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>-37.819744399999998</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>145.00502520000001</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>60</v>
       </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2">
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2">
         <v>5</v>
-      </c>
-      <c r="J2">
-        <v>98</v>
       </c>
       <c r="K2">
         <v>98</v>
       </c>
-      <c r="L2" s="1">
-        <f>((((3*J2)+(2*K2))-(5*I2))/495)*100</f>
+      <c r="L2">
+        <v>98</v>
+      </c>
+      <c r="M2" s="1">
+        <f t="shared" ref="M2:M38" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
         <v>93.939393939393938</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -944,35 +972,38 @@
         <v>35</v>
       </c>
       <c r="D3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" t="s">
         <v>107</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>-37.816214700000003</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>144.96879939999999</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>61</v>
       </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3">
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3">
         <v>5</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>96</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>98</v>
       </c>
-      <c r="L3" s="1">
-        <f>((((3*J3)+(2*K3))-(5*I3))/495)*100</f>
+      <c r="M3" s="1">
+        <f t="shared" si="1"/>
         <v>92.72727272727272</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -984,35 +1015,38 @@
         <v>32</v>
       </c>
       <c r="D4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" t="s">
         <v>108</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>-37.855813300000001</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>145.02494609999999</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>62</v>
       </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4">
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4">
         <v>5</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>97</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>98</v>
       </c>
-      <c r="L4" s="1">
-        <f>((((3*J4)+(2*K4))-(5*I4))/495)*100</f>
+      <c r="M4" s="1">
+        <f t="shared" si="1"/>
         <v>93.333333333333329</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1024,35 +1058,38 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" t="s">
         <v>109</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>-37.815699100000003</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>144.97141070000001</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>63</v>
       </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5">
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5">
         <v>3.5</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>93</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>94</v>
       </c>
-      <c r="L5" s="1">
-        <f>((((3*J5)+(2*K5))-(5*I5))/495)*100</f>
+      <c r="M5" s="1">
+        <f t="shared" si="1"/>
         <v>90.808080808080803</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1064,35 +1101,38 @@
         <v>28</v>
       </c>
       <c r="D6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" t="s">
         <v>141</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>-37.812163599999998</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>144.97241320000001</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>64</v>
       </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6">
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6">
         <v>4.5</v>
-      </c>
-      <c r="J6">
-        <v>94</v>
       </c>
       <c r="K6">
         <v>94</v>
       </c>
-      <c r="L6" s="1">
-        <f>((((3*J6)+(2*K6))-(5*I6))/495)*100</f>
+      <c r="L6">
+        <v>94</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" si="1"/>
         <v>90.404040404040416</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1104,35 +1144,38 @@
         <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" t="s">
         <v>110</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-37.816716700000001</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>144.96914169999999</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>65</v>
       </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7">
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7">
         <v>4</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>94</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>90</v>
       </c>
-      <c r="L7" s="1">
-        <f>((((3*J7)+(2*K7))-(5*I7))/495)*100</f>
+      <c r="M7" s="1">
+        <f t="shared" si="1"/>
         <v>89.292929292929287</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1144,35 +1187,38 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" t="s">
         <v>111</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>-37.816099999999999</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>144.96879939999999</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>61</v>
       </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8">
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8">
         <v>4.5</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>95</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>90</v>
       </c>
-      <c r="L8" s="1">
-        <f>((((3*J8)+(2*K8))-(5*I8))/495)*100</f>
+      <c r="M8" s="1">
+        <f t="shared" si="1"/>
         <v>89.393939393939391</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1184,35 +1230,38 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" t="s">
         <v>142</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>-37.814523000000001</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>144.974164</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>66</v>
       </c>
-      <c r="H9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9">
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9">
         <v>2.5</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>89</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>90</v>
       </c>
-      <c r="L9" s="1">
-        <f>((((3*J9)+(2*K9))-(5*I9))/495)*100</f>
+      <c r="M9" s="1">
+        <f t="shared" si="1"/>
         <v>87.777777777777771</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1224,35 +1273,38 @@
         <v>29</v>
       </c>
       <c r="D10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E10" t="s">
         <v>112</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-37.813552199999997</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>144.9619835</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>67</v>
       </c>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10">
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10">
         <v>4</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>92</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>90</v>
       </c>
-      <c r="L10" s="1">
-        <f>((((3*J10)+(2*K10))-(5*I10))/495)*100</f>
+      <c r="M10" s="1">
+        <f t="shared" si="1"/>
         <v>88.080808080808083</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1264,35 +1316,38 @@
         <v>38</v>
       </c>
       <c r="D11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" t="s">
         <v>113</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>-37.813279100000003</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>144.96851409999999</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>68</v>
       </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11">
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11">
         <v>4</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>89</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>92</v>
       </c>
-      <c r="L11" s="1">
-        <f>((((3*J11)+(2*K11))-(5*I11))/495)*100</f>
+      <c r="M11" s="1">
+        <f t="shared" si="1"/>
         <v>87.070707070707059</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -1304,35 +1359,38 @@
         <v>31</v>
       </c>
       <c r="D12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" t="s">
         <v>114</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-37.815992799999997</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>144.96995380000001</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>69</v>
       </c>
-      <c r="H12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12">
+      <c r="I12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12">
         <v>3.5</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>89</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>90</v>
       </c>
-      <c r="L12" s="1">
-        <f>((((3*J12)+(2*K12))-(5*I12))/495)*100</f>
+      <c r="M12" s="1">
+        <f t="shared" si="1"/>
         <v>86.767676767676775</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -1344,35 +1402,38 @@
         <v>36</v>
       </c>
       <c r="D13" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13" t="s">
         <v>115</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>-37.8181528</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>144.96266199999999</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>70</v>
       </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13">
+      <c r="I13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13">
         <v>5</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>92</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>88</v>
       </c>
-      <c r="L13" s="1">
-        <f>((((3*J13)+(2*K13))-(5*I13))/495)*100</f>
+      <c r="M13" s="1">
+        <f t="shared" si="1"/>
         <v>86.26262626262627</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1384,35 +1445,38 @@
         <v>46</v>
       </c>
       <c r="D14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" t="s">
         <v>116</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>-37.813893700000001</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>144.96168950000001</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>71</v>
       </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14">
+      <c r="I14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14">
         <v>4</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>90</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>89</v>
       </c>
-      <c r="L14" s="1">
-        <f>((((3*J14)+(2*K14))-(5*I14))/495)*100</f>
+      <c r="M14" s="1">
+        <f t="shared" si="1"/>
         <v>86.464646464646464</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1424,35 +1488,38 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" t="s">
         <v>117</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>-37.815804300000003</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>144.97253459999999</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>72</v>
       </c>
-      <c r="H15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15">
+      <c r="I15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15">
         <v>4</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>87</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>89</v>
       </c>
-      <c r="L15" s="1">
-        <f>((((3*J15)+(2*K15))-(5*I15))/495)*100</f>
+      <c r="M15" s="1">
+        <f t="shared" si="1"/>
         <v>84.646464646464651</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1464,35 +1531,38 @@
         <v>41</v>
       </c>
       <c r="D16" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" t="s">
         <v>118</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-37.815840299999998</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>144.9710359</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>73</v>
       </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16">
+      <c r="I16" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16">
         <v>3.5</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>89</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>85</v>
       </c>
-      <c r="L16" s="1">
-        <f>((((3*J16)+(2*K16))-(5*I16))/495)*100</f>
+      <c r="M16" s="1">
+        <f t="shared" si="1"/>
         <v>84.747474747474755</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1504,35 +1574,38 @@
         <v>34</v>
       </c>
       <c r="D17" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" t="s">
         <v>119</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>-37.805473399999997</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>144.97585419999999</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>75</v>
       </c>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17">
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17">
         <v>4</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>89</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>87</v>
       </c>
-      <c r="L17" s="1">
-        <f>((((3*J17)+(2*K17))-(5*I17))/495)*100</f>
+      <c r="M17" s="1">
+        <f t="shared" si="1"/>
         <v>85.050505050505052</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -1544,35 +1617,38 @@
         <v>30</v>
       </c>
       <c r="D18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" t="s">
         <v>120</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>-37.813394000000002</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>144.9686092</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>76</v>
       </c>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18">
+      <c r="I18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18">
         <v>4</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>90</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>86</v>
       </c>
-      <c r="L18" s="1">
-        <f>((((3*J18)+(2*K18))-(5*I18))/495)*100</f>
+      <c r="M18" s="1">
+        <f t="shared" si="1"/>
         <v>85.25252525252526</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1584,35 +1660,38 @@
         <v>32</v>
       </c>
       <c r="D19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" t="s">
         <v>121</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>-37.814913199999999</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>144.97312289999999</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>77</v>
       </c>
-      <c r="H19" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19">
+      <c r="I19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19">
         <v>3.5</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>90</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>85</v>
       </c>
-      <c r="L19" s="1">
-        <f>((((3*J19)+(2*K19))-(5*I19))/495)*100</f>
+      <c r="M19" s="1">
+        <f t="shared" si="1"/>
         <v>85.353535353535349</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1624,35 +1703,38 @@
         <v>32</v>
       </c>
       <c r="D20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" t="s">
         <v>122</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>-37.815887199999999</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>144.96873160000001</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>78</v>
       </c>
-      <c r="H20" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20">
+      <c r="I20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20">
         <v>4</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>86</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>89</v>
       </c>
-      <c r="L20" s="1">
-        <f>((((3*J20)+(2*K20))-(5*I20))/495)*100</f>
+      <c r="M20" s="1">
+        <f t="shared" si="1"/>
         <v>84.040404040404042</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1664,35 +1746,38 @@
         <v>36</v>
       </c>
       <c r="D21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" t="s">
         <v>123</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>-37.816189100000003</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>144.9683115</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>79</v>
       </c>
-      <c r="H21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21">
+      <c r="I21" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21">
         <v>4</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>87</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>88</v>
       </c>
-      <c r="L21" s="1">
-        <f>((((3*J21)+(2*K21))-(5*I21))/495)*100</f>
+      <c r="M21" s="1">
+        <f t="shared" si="1"/>
         <v>84.242424242424235</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1704,35 +1789,38 @@
         <v>32</v>
       </c>
       <c r="D22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" t="s">
         <v>124</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-37.805464999999998</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>144.97589930000001</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>74</v>
       </c>
-      <c r="H22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22">
+      <c r="I22" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22">
         <v>3.5</v>
-      </c>
-      <c r="J22">
-        <v>87</v>
       </c>
       <c r="K22">
         <v>87</v>
       </c>
-      <c r="L22" s="1">
-        <f>((((3*J22)+(2*K22))-(5*I22))/495)*100</f>
+      <c r="L22">
+        <v>87</v>
+      </c>
+      <c r="M22" s="1">
+        <f t="shared" si="1"/>
         <v>84.343434343434339</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -1744,35 +1832,38 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" t="s">
         <v>125</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>-37.8063845</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>144.98510970000001</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>80</v>
       </c>
-      <c r="H23" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23">
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23">
         <v>3.5</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>84</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>88</v>
       </c>
-      <c r="L23" s="1">
-        <f>((((3*J23)+(2*K23))-(5*I23))/495)*100</f>
+      <c r="M23" s="1">
+        <f t="shared" si="1"/>
         <v>82.929292929292927</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -1784,35 +1875,38 @@
         <v>45</v>
       </c>
       <c r="D24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" t="s">
         <v>126</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>-37.795028600000002</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>144.9792506</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>81</v>
       </c>
-      <c r="H24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I24">
+      <c r="I24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24">
         <v>3.5</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>90</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>80</v>
       </c>
-      <c r="L24" s="1">
-        <f>((((3*J24)+(2*K24))-(5*I24))/495)*100</f>
+      <c r="M24" s="1">
+        <f t="shared" si="1"/>
         <v>83.333333333333343</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1824,35 +1918,38 @@
         <v>37</v>
       </c>
       <c r="D25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E25" t="s">
         <v>127</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>-37.8136394</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>144.9733909</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>82</v>
       </c>
-      <c r="H25" t="s">
-        <v>27</v>
-      </c>
-      <c r="I25">
+      <c r="I25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25">
         <v>3.5</v>
-      </c>
-      <c r="J25">
-        <v>85</v>
       </c>
       <c r="K25">
         <v>85</v>
       </c>
-      <c r="L25" s="1">
-        <f>((((3*J25)+(2*K25))-(5*I25))/495)*100</f>
+      <c r="L25">
+        <v>85</v>
+      </c>
+      <c r="M25" s="1">
+        <f t="shared" si="1"/>
         <v>82.323232323232318</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>84</v>
       </c>
@@ -1864,35 +1961,38 @@
         <v>30</v>
       </c>
       <c r="D26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" t="s">
         <v>128</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>-37.864322399999999</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>144.98226339999999</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>83</v>
       </c>
-      <c r="H26" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26">
+      <c r="I26" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26">
         <v>2.5</v>
-      </c>
-      <c r="J26">
-        <v>84</v>
       </c>
       <c r="K26">
         <v>84</v>
       </c>
-      <c r="L26" s="1">
-        <f>((((3*J26)+(2*K26))-(5*I26))/495)*100</f>
+      <c r="L26">
+        <v>84</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="1"/>
         <v>82.323232323232318</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1904,35 +2004,38 @@
         <v>34</v>
       </c>
       <c r="D27" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" t="s">
         <v>129</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>-37.849426999999999</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>144.99151900000001</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>85</v>
       </c>
-      <c r="H27" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27">
+      <c r="I27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27">
         <v>3.5</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>80</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>88</v>
       </c>
-      <c r="L27" s="1">
-        <f>((((3*J27)+(2*K27))-(5*I27))/495)*100</f>
+      <c r="M27" s="1">
+        <f t="shared" si="1"/>
         <v>80.505050505050505</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -1944,35 +2047,38 @@
         <v>30</v>
       </c>
       <c r="D28" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" t="s">
         <v>130</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>-37.810980200000003</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>144.97253789999999</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>86</v>
       </c>
-      <c r="H28" t="s">
-        <v>27</v>
-      </c>
-      <c r="I28">
+      <c r="I28" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28">
         <v>3</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>86</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>78</v>
       </c>
-      <c r="L28" s="1">
-        <f>((((3*J28)+(2*K28))-(5*I28))/495)*100</f>
+      <c r="M28" s="1">
+        <f t="shared" si="1"/>
         <v>80.606060606060609</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1984,35 +2090,38 @@
         <v>37</v>
       </c>
       <c r="D29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29" t="s">
         <v>131</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>-37.816451299999997</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>144.96909969999999</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>87</v>
       </c>
-      <c r="H29" t="s">
-        <v>27</v>
-      </c>
-      <c r="I29">
+      <c r="I29" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29">
         <v>3.5</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>83</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>85</v>
       </c>
-      <c r="L29" s="1">
-        <f>((((3*J29)+(2*K29))-(5*I29))/495)*100</f>
+      <c r="M29" s="1">
+        <f t="shared" si="1"/>
         <v>81.111111111111114</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -2024,35 +2133,38 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
+        <v>149</v>
+      </c>
+      <c r="E30" t="s">
         <v>132</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>-37.788539800000002</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>144.9318371</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>88</v>
       </c>
-      <c r="H30" t="s">
-        <v>27</v>
-      </c>
-      <c r="I30">
+      <c r="I30" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30">
         <v>2</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>84</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>80</v>
       </c>
-      <c r="L30" s="1">
-        <f>((((3*J30)+(2*K30))-(5*I30))/495)*100</f>
+      <c r="M30" s="1">
+        <f t="shared" si="1"/>
         <v>81.212121212121218</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>103</v>
       </c>
@@ -2064,35 +2176,38 @@
         <v>32</v>
       </c>
       <c r="D31" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" t="s">
         <v>133</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>-37.813554099999998</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>144.97102520000001</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>89</v>
       </c>
-      <c r="H31" t="s">
-        <v>27</v>
-      </c>
-      <c r="I31">
+      <c r="I31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31">
         <v>5</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>87</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>80</v>
       </c>
-      <c r="L31" s="1">
-        <f>((((3*J31)+(2*K31))-(5*I31))/495)*100</f>
+      <c r="M31" s="1">
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -2104,35 +2219,38 @@
         <v>42</v>
       </c>
       <c r="D32" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" t="s">
         <v>134</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>-37.810779599999996</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>144.97079550000001</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>90</v>
       </c>
-      <c r="H32" t="s">
-        <v>27</v>
-      </c>
-      <c r="I32">
+      <c r="I32" t="s">
+        <v>143</v>
+      </c>
+      <c r="J32">
         <v>3</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>80</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>82</v>
       </c>
-      <c r="L32" s="1">
-        <f>((((3*J32)+(2*K32))-(5*I32))/495)*100</f>
+      <c r="M32" s="1">
+        <f t="shared" si="1"/>
         <v>78.585858585858574</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -2144,35 +2262,38 @@
         <v>29</v>
       </c>
       <c r="D33" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" t="s">
         <v>135</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>-37.8150555</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>144.97252929999999</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>91</v>
       </c>
-      <c r="H33" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33">
+      <c r="I33" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33">
         <v>4</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>85</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>78</v>
       </c>
-      <c r="L33" s="1">
-        <f>((((3*J33)+(2*K33))-(5*I33))/495)*100</f>
+      <c r="M33" s="1">
+        <f t="shared" si="1"/>
         <v>78.98989898989899</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -2184,35 +2305,38 @@
         <v>29</v>
       </c>
       <c r="D34" t="s">
+        <v>148</v>
+      </c>
+      <c r="E34" t="s">
         <v>136</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>-37.815333000000003</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>144.96267309999999</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>92</v>
       </c>
-      <c r="H34" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34">
+      <c r="I34" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34">
         <v>4</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>80</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>84</v>
       </c>
-      <c r="L34" s="1">
-        <f>((((3*J34)+(2*K34))-(5*I34))/495)*100</f>
+      <c r="M34" s="1">
+        <f t="shared" si="1"/>
         <v>78.383838383838395</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -2224,35 +2348,38 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E35" t="s">
         <v>137</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>-37.815766099999998</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>144.96988970000001</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>94</v>
       </c>
-      <c r="H35" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35">
+      <c r="I35" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35">
         <v>3.5</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>82</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>74</v>
       </c>
-      <c r="L35" s="1">
-        <f>((((3*J35)+(2*K35))-(5*I35))/495)*100</f>
+      <c r="M35" s="1">
+        <f t="shared" si="1"/>
         <v>76.060606060606062</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>26</v>
       </c>
@@ -2264,35 +2391,38 @@
         <v>40</v>
       </c>
       <c r="D36" t="s">
+        <v>148</v>
+      </c>
+      <c r="E36" t="s">
         <v>138</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>-37.812815000000001</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>144.97251850000001</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>95</v>
       </c>
-      <c r="H36" t="s">
-        <v>27</v>
-      </c>
-      <c r="I36">
+      <c r="I36" t="s">
+        <v>27</v>
+      </c>
+      <c r="J36">
         <v>2.5</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>72</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>82</v>
       </c>
-      <c r="L36" s="1">
-        <f>((((3*J36)+(2*K36))-(5*I36))/495)*100</f>
+      <c r="M36" s="1">
+        <f t="shared" si="1"/>
         <v>74.242424242424249</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -2304,35 +2434,38 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" t="s">
         <v>139</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>-37.815731999999997</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>144.97268800000001</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>96</v>
       </c>
-      <c r="H37" t="s">
-        <v>27</v>
-      </c>
-      <c r="I37">
+      <c r="I37" t="s">
+        <v>27</v>
+      </c>
+      <c r="J37">
         <v>3</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>75</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>70</v>
       </c>
-      <c r="L37" s="1">
-        <f>((((3*J37)+(2*K37))-(5*I37))/495)*100</f>
+      <c r="M37" s="1">
+        <f t="shared" si="1"/>
         <v>70.707070707070713</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>97</v>
       </c>
@@ -2344,36 +2477,39 @@
         <v>29</v>
       </c>
       <c r="D38" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" t="s">
         <v>140</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>-37.814254800000001</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>144.974186</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>98</v>
       </c>
-      <c r="H38" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38">
+      <c r="I38" t="s">
+        <v>27</v>
+      </c>
+      <c r="J38">
         <v>4.5</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>70</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>60</v>
       </c>
-      <c r="L38" s="1">
-        <f>((((3*J38)+(2*K38))-(5*I38))/495)*100</f>
+      <c r="M38" s="1">
+        <f t="shared" si="1"/>
         <v>62.121212121212125</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L38">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M38">
     <sortCondition descending="1" ref="B2:B38"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED9DB3C8-DAE7-49AC-81DC-71A0B5FFEA17}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27DC611B-55D6-4EB0-A0B9-08F2EA56952E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="156">
   <si>
     <t>San Telmo</t>
   </si>
@@ -119,9 +119,6 @@
     <t>Bar Lourinha</t>
   </si>
   <si>
-    <t>Restaurant</t>
-  </si>
-  <si>
     <t>Argentinian</t>
   </si>
   <si>
@@ -467,9 +464,6 @@
     <t>Our local wine bar, newly opened. Still relatively cheap, cosy French bistro upstairs</t>
   </si>
   <si>
-    <t>Cocktail</t>
-  </si>
-  <si>
     <t>Region</t>
   </si>
   <si>
@@ -486,6 +480,30 @@
   </si>
   <si>
     <t>Middle East/Africa</t>
+  </si>
+  <si>
+    <t>Fine Dining</t>
+  </si>
+  <si>
+    <t>Dinner</t>
+  </si>
+  <si>
+    <t>Wine</t>
+  </si>
+  <si>
+    <t>Cocktails</t>
+  </si>
+  <si>
+    <t>Flower Drum</t>
+  </si>
+  <si>
+    <t>Cantonese</t>
+  </si>
+  <si>
+    <t>Really old school, fine dining cantonese restraurant. Incredibly tasty food.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/m1eqeSdwyasAyo3G8</t>
   </si>
 </sst>
 </file>
@@ -539,6 +557,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -858,14 +880,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFE0398-5E3D-42F9-829F-76BDA5454F49}">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.19921875" customWidth="1"/>
     <col min="2" max="2" width="9.59765625" customWidth="1"/>
     <col min="3" max="3" width="12.9296875" customWidth="1"/>
     <col min="4" max="4" width="14.19921875" customWidth="1"/>
-    <col min="5" max="5" width="66.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="66.3984375" customWidth="1"/>
     <col min="6" max="6" width="12.9296875" customWidth="1"/>
     <col min="7" max="7" width="17.265625" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" customWidth="1"/>
@@ -878,61 +900,61 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" t="s">
         <v>55</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="K1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1">
-        <f t="shared" ref="B2:B38" si="0">ROUND(M2,0)</f>
+        <f t="shared" ref="B2:B39" si="0">ROUND(M2,0)</f>
         <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F2">
         <v>-37.819744399999998</v>
@@ -941,10 +963,10 @@
         <v>145.00502520000001</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -956,26 +978,26 @@
         <v>98</v>
       </c>
       <c r="M2" s="1">
-        <f t="shared" ref="M2:M38" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
+        <f t="shared" ref="M2:M39" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
         <v>93.939393939393938</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" s="1">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F3">
         <v>-37.816214700000003</v>
@@ -984,10 +1006,10 @@
         <v>144.96879939999999</v>
       </c>
       <c r="H3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1005,20 +1027,20 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F4">
         <v>-37.855813300000001</v>
@@ -1027,10 +1049,10 @@
         <v>145.02494609999999</v>
       </c>
       <c r="H4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -1055,13 +1077,13 @@
         <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F5">
         <v>-37.815699100000003</v>
@@ -1070,10 +1092,10 @@
         <v>144.97141070000001</v>
       </c>
       <c r="H5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J5">
         <v>3.5</v>
@@ -1098,13 +1120,13 @@
         <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F6">
         <v>-37.812163599999998</v>
@@ -1113,10 +1135,10 @@
         <v>144.97241320000001</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J6">
         <v>4.5</v>
@@ -1141,13 +1163,13 @@
         <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F7">
         <v>-37.816716700000001</v>
@@ -1156,10 +1178,10 @@
         <v>144.96914169999999</v>
       </c>
       <c r="H7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -1184,13 +1206,13 @@
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F8">
         <v>-37.816099999999999</v>
@@ -1199,10 +1221,10 @@
         <v>144.96879939999999</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I8" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="J8">
         <v>4.5</v>
@@ -1227,13 +1249,13 @@
         <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F9">
         <v>-37.814523000000001</v>
@@ -1242,10 +1264,10 @@
         <v>144.974164</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="J9">
         <v>2.5</v>
@@ -1270,13 +1292,13 @@
         <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F10">
         <v>-37.813552199999997</v>
@@ -1285,10 +1307,10 @@
         <v>144.9619835</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -1313,13 +1335,13 @@
         <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F11">
         <v>-37.813279100000003</v>
@@ -1328,10 +1350,10 @@
         <v>144.96851409999999</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I11" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -1349,20 +1371,20 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F12">
         <v>-37.815992799999997</v>
@@ -1371,10 +1393,10 @@
         <v>144.96995380000001</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I12" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -1399,13 +1421,13 @@
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F13">
         <v>-37.8181528</v>
@@ -1414,10 +1436,10 @@
         <v>144.96266199999999</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1442,13 +1464,13 @@
         <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F14">
         <v>-37.813893700000001</v>
@@ -1457,10 +1479,10 @@
         <v>144.96168950000001</v>
       </c>
       <c r="H14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -1485,13 +1507,13 @@
         <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F15">
         <v>-37.815804300000003</v>
@@ -1500,10 +1522,10 @@
         <v>144.97253459999999</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -1528,13 +1550,13 @@
         <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F16">
         <v>-37.815840299999998</v>
@@ -1543,10 +1565,10 @@
         <v>144.9710359</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J16">
         <v>3.5</v>
@@ -1571,13 +1593,13 @@
         <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F17">
         <v>-37.805473399999997</v>
@@ -1586,10 +1608,10 @@
         <v>144.97585419999999</v>
       </c>
       <c r="H17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -1614,13 +1636,13 @@
         <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F18">
         <v>-37.813394000000002</v>
@@ -1629,10 +1651,10 @@
         <v>144.9686092</v>
       </c>
       <c r="H18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -1657,13 +1679,13 @@
         <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F19">
         <v>-37.814913199999999</v>
@@ -1672,10 +1694,10 @@
         <v>144.97312289999999</v>
       </c>
       <c r="H19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J19">
         <v>3.5</v>
@@ -1700,13 +1722,13 @@
         <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F20">
         <v>-37.815887199999999</v>
@@ -1715,10 +1737,10 @@
         <v>144.96873160000001</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -1743,13 +1765,13 @@
         <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F21">
         <v>-37.816189100000003</v>
@@ -1758,10 +1780,10 @@
         <v>144.9683115</v>
       </c>
       <c r="H21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I21" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -1786,13 +1808,13 @@
         <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F22">
         <v>-37.805464999999998</v>
@@ -1801,10 +1823,10 @@
         <v>144.97589930000001</v>
       </c>
       <c r="H22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J22">
         <v>3.5</v>
@@ -1829,13 +1851,13 @@
         <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F23">
         <v>-37.8063845</v>
@@ -1844,10 +1866,10 @@
         <v>144.98510970000001</v>
       </c>
       <c r="H23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J23">
         <v>3.5</v>
@@ -1872,13 +1894,13 @@
         <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F24">
         <v>-37.795028600000002</v>
@@ -1887,10 +1909,10 @@
         <v>144.9792506</v>
       </c>
       <c r="H24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J24">
         <v>3.5</v>
@@ -1915,13 +1937,13 @@
         <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F25">
         <v>-37.8136394</v>
@@ -1930,10 +1952,10 @@
         <v>144.9733909</v>
       </c>
       <c r="H25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I25" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J25">
         <v>3.5</v>
@@ -1951,20 +1973,20 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F26">
         <v>-37.864322399999999</v>
@@ -1973,10 +1995,10 @@
         <v>144.98226339999999</v>
       </c>
       <c r="H26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J26">
         <v>2.5</v>
@@ -2001,13 +2023,13 @@
         <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F27">
         <v>-37.849426999999999</v>
@@ -2016,10 +2038,10 @@
         <v>144.99151900000001</v>
       </c>
       <c r="H27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J27">
         <v>3.5</v>
@@ -2044,13 +2066,13 @@
         <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F28">
         <v>-37.810980200000003</v>
@@ -2059,10 +2081,10 @@
         <v>144.97253789999999</v>
       </c>
       <c r="H28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="J28">
         <v>3</v>
@@ -2087,13 +2109,13 @@
         <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F29">
         <v>-37.816451299999997</v>
@@ -2102,10 +2124,10 @@
         <v>144.96909969999999</v>
       </c>
       <c r="H29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I29" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J29">
         <v>3.5</v>
@@ -2123,20 +2145,20 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="1">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>50</v>
-      </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F30">
         <v>-37.788539800000002</v>
@@ -2145,10 +2167,10 @@
         <v>144.9318371</v>
       </c>
       <c r="H30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2166,20 +2188,20 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F31">
         <v>-37.813554099999998</v>
@@ -2188,10 +2210,10 @@
         <v>144.97102520000001</v>
       </c>
       <c r="H31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="J31">
         <v>5</v>
@@ -2216,13 +2238,13 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F32">
         <v>-37.810779599999996</v>
@@ -2231,10 +2253,10 @@
         <v>144.97079550000001</v>
       </c>
       <c r="H32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -2252,20 +2274,20 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F33">
         <v>-37.8150555</v>
@@ -2274,10 +2296,10 @@
         <v>144.97252929999999</v>
       </c>
       <c r="H33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -2295,20 +2317,20 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F34">
         <v>-37.815333000000003</v>
@@ -2317,10 +2339,10 @@
         <v>144.96267309999999</v>
       </c>
       <c r="H34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J34">
         <v>4</v>
@@ -2345,13 +2367,13 @@
         <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F35">
         <v>-37.815766099999998</v>
@@ -2360,10 +2382,10 @@
         <v>144.96988970000001</v>
       </c>
       <c r="H35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I35" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J35">
         <v>3.5</v>
@@ -2388,13 +2410,13 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F36">
         <v>-37.812815000000001</v>
@@ -2403,10 +2425,10 @@
         <v>144.97251850000001</v>
       </c>
       <c r="H36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J36">
         <v>2.5</v>
@@ -2431,13 +2453,13 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F37">
         <v>-37.815731999999997</v>
@@ -2446,10 +2468,10 @@
         <v>144.97268800000001</v>
       </c>
       <c r="H37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I37" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2467,20 +2489,20 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B38" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38">
         <v>-37.814254800000001</v>
@@ -2489,10 +2511,10 @@
         <v>144.974186</v>
       </c>
       <c r="H38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I38" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="J38">
         <v>4.5</v>
@@ -2506,6 +2528,49 @@
       <c r="M38" s="1">
         <f t="shared" si="1"/>
         <v>62.121212121212125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="1">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39">
+        <v>-37.811877199999998</v>
+      </c>
+      <c r="G39">
+        <v>144.96924580000001</v>
+      </c>
+      <c r="H39" t="s">
+        <v>155</v>
+      </c>
+      <c r="I39" t="s">
+        <v>148</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
+      <c r="K39">
+        <v>90</v>
+      </c>
+      <c r="L39">
+        <v>92</v>
+      </c>
+      <c r="M39" s="1">
+        <f t="shared" si="1"/>
+        <v>86.666666666666671</v>
       </c>
     </row>
   </sheetData>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27DC611B-55D6-4EB0-A0B9-08F2EA56952E}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42608C19-0DBF-4080-AF62-8F074858D5E2}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>Serai</t>
   </si>
   <si>
-    <t>Tipo 0.0</t>
-  </si>
-  <si>
     <t>Entrecote</t>
   </si>
   <si>
@@ -504,6 +501,9 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/m1eqeSdwyasAyo3G8</t>
+  </si>
+  <si>
+    <t>Tipo 00</t>
   </si>
 </sst>
 </file>
@@ -557,10 +557,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -900,61 +896,61 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" t="s">
         <v>54</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="K1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1">
         <f t="shared" ref="B2:B39" si="0">ROUND(M2,0)</f>
         <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2">
         <v>-37.819744399999998</v>
@@ -963,10 +959,10 @@
         <v>145.00502520000001</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -984,20 +980,20 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" s="1">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F3">
         <v>-37.816214700000003</v>
@@ -1006,10 +1002,10 @@
         <v>144.96879939999999</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1027,20 +1023,20 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F4">
         <v>-37.855813300000001</v>
@@ -1049,10 +1045,10 @@
         <v>145.02494609999999</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -1077,13 +1073,13 @@
         <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F5">
         <v>-37.815699100000003</v>
@@ -1092,10 +1088,10 @@
         <v>144.97141070000001</v>
       </c>
       <c r="H5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J5">
         <v>3.5</v>
@@ -1120,13 +1116,13 @@
         <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F6">
         <v>-37.812163599999998</v>
@@ -1135,10 +1131,10 @@
         <v>144.97241320000001</v>
       </c>
       <c r="H6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J6">
         <v>4.5</v>
@@ -1163,13 +1159,13 @@
         <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F7">
         <v>-37.816716700000001</v>
@@ -1178,10 +1174,10 @@
         <v>144.96914169999999</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -1206,13 +1202,13 @@
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F8">
         <v>-37.816099999999999</v>
@@ -1221,10 +1217,10 @@
         <v>144.96879939999999</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J8">
         <v>4.5</v>
@@ -1249,13 +1245,13 @@
         <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F9">
         <v>-37.814523000000001</v>
@@ -1264,10 +1260,10 @@
         <v>144.974164</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J9">
         <v>2.5</v>
@@ -1285,20 +1281,20 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>155</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F10">
         <v>-37.813552199999997</v>
@@ -1307,10 +1303,10 @@
         <v>144.9619835</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -1335,13 +1331,13 @@
         <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F11">
         <v>-37.813279100000003</v>
@@ -1350,10 +1346,10 @@
         <v>144.96851409999999</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -1371,20 +1367,20 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F12">
         <v>-37.815992799999997</v>
@@ -1393,10 +1389,10 @@
         <v>144.96995380000001</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -1421,13 +1417,13 @@
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F13">
         <v>-37.8181528</v>
@@ -1436,10 +1432,10 @@
         <v>144.96266199999999</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1464,13 +1460,13 @@
         <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F14">
         <v>-37.813893700000001</v>
@@ -1479,10 +1475,10 @@
         <v>144.96168950000001</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -1507,13 +1503,13 @@
         <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F15">
         <v>-37.815804300000003</v>
@@ -1522,10 +1518,10 @@
         <v>144.97253459999999</v>
       </c>
       <c r="H15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -1550,13 +1546,13 @@
         <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F16">
         <v>-37.815840299999998</v>
@@ -1565,10 +1561,10 @@
         <v>144.9710359</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J16">
         <v>3.5</v>
@@ -1586,20 +1582,20 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F17">
         <v>-37.805473399999997</v>
@@ -1608,10 +1604,10 @@
         <v>144.97585419999999</v>
       </c>
       <c r="H17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -1636,13 +1632,13 @@
         <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F18">
         <v>-37.813394000000002</v>
@@ -1651,10 +1647,10 @@
         <v>144.9686092</v>
       </c>
       <c r="H18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -1679,13 +1675,13 @@
         <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F19">
         <v>-37.814913199999999</v>
@@ -1694,10 +1690,10 @@
         <v>144.97312289999999</v>
       </c>
       <c r="H19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J19">
         <v>3.5</v>
@@ -1722,13 +1718,13 @@
         <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F20">
         <v>-37.815887199999999</v>
@@ -1737,10 +1733,10 @@
         <v>144.96873160000001</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -1765,13 +1761,13 @@
         <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F21">
         <v>-37.816189100000003</v>
@@ -1780,10 +1776,10 @@
         <v>144.9683115</v>
       </c>
       <c r="H21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -1801,20 +1797,20 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F22">
         <v>-37.805464999999998</v>
@@ -1823,10 +1819,10 @@
         <v>144.97589930000001</v>
       </c>
       <c r="H22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J22">
         <v>3.5</v>
@@ -1844,20 +1840,20 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F23">
         <v>-37.8063845</v>
@@ -1866,10 +1862,10 @@
         <v>144.98510970000001</v>
       </c>
       <c r="H23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J23">
         <v>3.5</v>
@@ -1887,20 +1883,20 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F24">
         <v>-37.795028600000002</v>
@@ -1909,10 +1905,10 @@
         <v>144.9792506</v>
       </c>
       <c r="H24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J24">
         <v>3.5</v>
@@ -1937,13 +1933,13 @@
         <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F25">
         <v>-37.8136394</v>
@@ -1952,10 +1948,10 @@
         <v>144.9733909</v>
       </c>
       <c r="H25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J25">
         <v>3.5</v>
@@ -1973,20 +1969,20 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F26">
         <v>-37.864322399999999</v>
@@ -1995,10 +1991,10 @@
         <v>144.98226339999999</v>
       </c>
       <c r="H26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J26">
         <v>2.5</v>
@@ -2016,20 +2012,20 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F27">
         <v>-37.849426999999999</v>
@@ -2038,10 +2034,10 @@
         <v>144.99151900000001</v>
       </c>
       <c r="H27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J27">
         <v>3.5</v>
@@ -2059,20 +2055,20 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F28">
         <v>-37.810980200000003</v>
@@ -2081,10 +2077,10 @@
         <v>144.97253789999999</v>
       </c>
       <c r="H28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J28">
         <v>3</v>
@@ -2109,13 +2105,13 @@
         <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F29">
         <v>-37.816451299999997</v>
@@ -2124,10 +2120,10 @@
         <v>144.96909969999999</v>
       </c>
       <c r="H29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J29">
         <v>3.5</v>
@@ -2145,20 +2141,20 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="1">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>49</v>
-      </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F30">
         <v>-37.788539800000002</v>
@@ -2167,10 +2163,10 @@
         <v>144.9318371</v>
       </c>
       <c r="H30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2188,20 +2184,20 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F31">
         <v>-37.813554099999998</v>
@@ -2210,10 +2206,10 @@
         <v>144.97102520000001</v>
       </c>
       <c r="H31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J31">
         <v>5</v>
@@ -2231,20 +2227,20 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" s="1">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F32">
         <v>-37.810779599999996</v>
@@ -2253,10 +2249,10 @@
         <v>144.97079550000001</v>
       </c>
       <c r="H32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -2274,20 +2270,20 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F33">
         <v>-37.8150555</v>
@@ -2296,10 +2292,10 @@
         <v>144.97252929999999</v>
       </c>
       <c r="H33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -2317,20 +2313,20 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B34" s="1">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34">
         <v>-37.815333000000003</v>
@@ -2339,10 +2335,10 @@
         <v>144.96267309999999</v>
       </c>
       <c r="H34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J34">
         <v>4</v>
@@ -2360,20 +2356,20 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="1">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35">
         <v>-37.815766099999998</v>
@@ -2382,10 +2378,10 @@
         <v>144.96988970000001</v>
       </c>
       <c r="H35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J35">
         <v>3.5</v>
@@ -2403,20 +2399,20 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B36" s="1">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36">
         <v>-37.812815000000001</v>
@@ -2425,10 +2421,10 @@
         <v>144.97251850000001</v>
       </c>
       <c r="H36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J36">
         <v>2.5</v>
@@ -2446,20 +2442,20 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" s="1">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F37">
         <v>-37.815731999999997</v>
@@ -2468,10 +2464,10 @@
         <v>144.97268800000001</v>
       </c>
       <c r="H37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2489,20 +2485,20 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B38" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F38">
         <v>-37.814254800000001</v>
@@ -2511,10 +2507,10 @@
         <v>144.974186</v>
       </c>
       <c r="H38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J38">
         <v>4.5</v>
@@ -2532,20 +2528,20 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="1">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
         <v>152</v>
       </c>
-      <c r="B39" s="1">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" t="s">
         <v>153</v>
-      </c>
-      <c r="D39" t="s">
-        <v>143</v>
-      </c>
-      <c r="E39" t="s">
-        <v>154</v>
       </c>
       <c r="F39">
         <v>-37.811877199999998</v>
@@ -2554,10 +2550,10 @@
         <v>144.96924580000001</v>
       </c>
       <c r="H39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J39">
         <v>5</v>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42608C19-0DBF-4080-AF62-8F074858D5E2}"/>
+  <xr:revisionPtr revIDLastSave="572" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{903A2D98-9FBF-4658-A2B7-AEDDC78ABB62}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="246">
   <si>
     <t>San Telmo</t>
   </si>
@@ -383,9 +383,6 @@
     <t>Not strictly speaking Filipino food I'm told but very tasty/different all the same</t>
   </si>
   <si>
-    <t>Plenty of tast meat and sushi. Very cool décor</t>
-  </si>
-  <si>
     <t>Lots of tasty, spicy deliciousness</t>
   </si>
   <si>
@@ -504,6 +501,279 @@
   </si>
   <si>
     <t>Tipo 00</t>
+  </si>
+  <si>
+    <t>Hochi Mama</t>
+  </si>
+  <si>
+    <t>Trendy, tasty asian fusion. Great place to start a night out.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/hi7h4EjotMU4c13bA</t>
+  </si>
+  <si>
+    <t>Hakata Gensuke</t>
+  </si>
+  <si>
+    <t>Quick, tasty ramen. Signature Pork Tonkotsu</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FPtD7z9TxMcbDKTz9</t>
+  </si>
+  <si>
+    <t>Ramen</t>
+  </si>
+  <si>
+    <t>Mensho</t>
+  </si>
+  <si>
+    <t>Tasty ramen but Hakata nextdoor is nicer.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/qkmttrsU6koRwq139</t>
+  </si>
+  <si>
+    <t>Udon Izakaya Maedaya</t>
+  </si>
+  <si>
+    <t>Simple ramen spot</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/PsvStDr3rBccTvFo6</t>
+  </si>
+  <si>
+    <t>Sot</t>
+  </si>
+  <si>
+    <t>Korean</t>
+  </si>
+  <si>
+    <t>Tidy little Korean restaurant</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8dYw14QDbMo5pYMQ9</t>
+  </si>
+  <si>
+    <t>Juicy Bao</t>
+  </si>
+  <si>
+    <t>Chinese</t>
+  </si>
+  <si>
+    <t>Really tasty dumpling spot, always busy</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nFrLzseyM4BaxWb36</t>
+  </si>
+  <si>
+    <t>OMI 380</t>
+  </si>
+  <si>
+    <t>High quality quick Japanese</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/hskBiGKLdPLEMNLr8</t>
+  </si>
+  <si>
+    <t>Vacation</t>
+  </si>
+  <si>
+    <t>Café and Roaster, really good coffee</t>
+  </si>
+  <si>
+    <t>Café</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JZ7nFvnsvQhdrsfKA</t>
+  </si>
+  <si>
+    <t>Tom Thumb</t>
+  </si>
+  <si>
+    <t>Really good coffee, weekdays only</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FxUdLgdgxzgL9zJJ9</t>
+  </si>
+  <si>
+    <t>Café Kinetic</t>
+  </si>
+  <si>
+    <t>Really quick, high quality breakfast. Weekdays only</t>
+  </si>
+  <si>
+    <t>Brunch</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BZZ65dP5yDMNrbNi6</t>
+  </si>
+  <si>
+    <t>Chin Chin</t>
+  </si>
+  <si>
+    <t>Very popular spot, large menu. Probably overrated</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/XPzEH38UM5S7da377</t>
+  </si>
+  <si>
+    <t>Supernormal</t>
+  </si>
+  <si>
+    <t>Very popular spot, large menu. Probably overrated, great for groups</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ZK3Mpg3jTUHG2gBC6</t>
+  </si>
+  <si>
+    <t>Agathe</t>
+  </si>
+  <si>
+    <t>Unbelievable pastries, pandan croissant is a must. Also in South Melbourne Market</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/dpCG4735kN8cPFD86</t>
+  </si>
+  <si>
+    <t>Apollo Inn</t>
+  </si>
+  <si>
+    <t>Very cosy cocktail bar, associated with Gimlet next door</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2DiLGt4nnzw4DDMD7</t>
+  </si>
+  <si>
+    <t>Really nice whiskey bar, huge selection</t>
+  </si>
+  <si>
+    <t>Bar</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/sCvB7a2a9vqb23y58</t>
+  </si>
+  <si>
+    <t>Whisky Den</t>
+  </si>
+  <si>
+    <t>Whisky and Alement</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/h4a6oen8vnUDEjoD7</t>
+  </si>
+  <si>
+    <t>Great Whisky bar, whisky tasting classes upstairs</t>
+  </si>
+  <si>
+    <t>The Meatball and Wine Bar</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Hy7tJrTEkmxu6inCA</t>
+  </si>
+  <si>
+    <t>Really simple menu, incredbily tasty. Great for a quick bite</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/U3E6Xd7mmZMFjMKw5</t>
+  </si>
+  <si>
+    <t>Beneath Driver Lane</t>
+  </si>
+  <si>
+    <t>Really trend Jazz and Whisky bar</t>
+  </si>
+  <si>
+    <t>Hectors Deli</t>
+  </si>
+  <si>
+    <t>Best sandwiches in Melbourne</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1xvKmea1kiJLKABm8</t>
+  </si>
+  <si>
+    <t>Lunch</t>
+  </si>
+  <si>
+    <t>Raya</t>
+  </si>
+  <si>
+    <t>Handy spot for a sandwich and coffee</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/gvFMdWq79vgeUpru5</t>
+  </si>
+  <si>
+    <t>Warkop</t>
+  </si>
+  <si>
+    <t>Indonesian</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/TA1eYrf4RopcCH4M7</t>
+  </si>
+  <si>
+    <t>Great sandwiches and bacon &amp; egg if you're early enough.</t>
+  </si>
+  <si>
+    <t>Butchers Diner</t>
+  </si>
+  <si>
+    <t>High-end chipper. Amazing burgers and toasties for the end of a night out</t>
+  </si>
+  <si>
+    <t>Quick Eats</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/TL8r1t6cWu3DXyjFA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1R5LNXnBeD22U3Ef9</t>
+  </si>
+  <si>
+    <t>Roccos Bologna Discoteca</t>
+  </si>
+  <si>
+    <t>Unreal Meatball Sub</t>
+  </si>
+  <si>
+    <t>Roccella</t>
+  </si>
+  <si>
+    <t>Really nice italian, loads of seats, great pizza</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/bhtsA4nAYEpJfwAd6</t>
+  </si>
+  <si>
+    <t>Prince Alfred</t>
+  </si>
+  <si>
+    <t>Large pub with nice beer garden. Great for groups</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/K9N6M65H5WWw6VBQ8</t>
+  </si>
+  <si>
+    <t>Humble Rays</t>
+  </si>
+  <si>
+    <t>Great Brunch spot, super fancy eggs benedict</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/cbuR6ZG3AHkFScYUA</t>
+  </si>
+  <si>
+    <t>Maverick</t>
+  </si>
+  <si>
+    <t>Tasty Brunch spot</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3X7G9zPVmJGrDKBZ6</t>
+  </si>
+  <si>
+    <t>Plenty of tasty  meat and sushi. Very cool décor</t>
   </si>
 </sst>
 </file>
@@ -876,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFE0398-5E3D-42F9-829F-76BDA5454F49}">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.19921875" customWidth="1"/>
@@ -886,7 +1156,7 @@
     <col min="5" max="5" width="66.3984375" customWidth="1"/>
     <col min="6" max="6" width="12.9296875" customWidth="1"/>
     <col min="7" max="7" width="17.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="29.19921875" customWidth="1"/>
     <col min="9" max="9" width="11.59765625" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="10.06640625" customWidth="1"/>
@@ -905,7 +1175,7 @@
         <v>99</v>
       </c>
       <c r="D1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E1" t="s">
         <v>52</v>
@@ -940,14 +1210,14 @@
         <v>45</v>
       </c>
       <c r="B2" s="1">
-        <f t="shared" ref="B2:B39" si="0">ROUND(M2,0)</f>
+        <f t="shared" ref="B2:B66" si="0">ROUND(M2,0)</f>
         <v>94</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
         <v>104</v>
@@ -962,7 +1232,7 @@
         <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -974,7 +1244,7 @@
         <v>98</v>
       </c>
       <c r="M2" s="1">
-        <f t="shared" ref="M2:M39" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
+        <f t="shared" ref="M2:M66" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
         <v>93.939393939393938</v>
       </c>
     </row>
@@ -990,7 +1260,7 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
         <v>105</v>
@@ -1005,7 +1275,7 @@
         <v>59</v>
       </c>
       <c r="I3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1033,7 +1303,7 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s">
         <v>106</v>
@@ -1048,7 +1318,7 @@
         <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -1076,7 +1346,7 @@
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
         <v>107</v>
@@ -1091,7 +1361,7 @@
         <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J5">
         <v>3.5</v>
@@ -1119,10 +1389,10 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F6">
         <v>-37.812163599999998</v>
@@ -1134,7 +1404,7 @@
         <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J6">
         <v>4.5</v>
@@ -1162,7 +1432,7 @@
         <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
         <v>108</v>
@@ -1177,7 +1447,7 @@
         <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -1205,7 +1475,7 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
         <v>109</v>
@@ -1220,7 +1490,7 @@
         <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J8">
         <v>4.5</v>
@@ -1248,10 +1518,10 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F9">
         <v>-37.814523000000001</v>
@@ -1263,7 +1533,7 @@
         <v>64</v>
       </c>
       <c r="I9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J9">
         <v>2.5</v>
@@ -1281,7 +1551,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
@@ -1291,7 +1561,7 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
         <v>110</v>
@@ -1306,7 +1576,7 @@
         <v>65</v>
       </c>
       <c r="I10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -1334,7 +1604,7 @@
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
         <v>111</v>
@@ -1349,7 +1619,7 @@
         <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -1377,7 +1647,7 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
         <v>112</v>
@@ -1392,7 +1662,7 @@
         <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -1420,7 +1690,7 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>113</v>
@@ -1435,7 +1705,7 @@
         <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1463,7 +1733,7 @@
         <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E14" t="s">
         <v>114</v>
@@ -1478,7 +1748,7 @@
         <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -1506,10 +1776,10 @@
         <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E15" t="s">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="F15">
         <v>-37.815804300000003</v>
@@ -1521,7 +1791,7 @@
         <v>70</v>
       </c>
       <c r="I15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -1549,10 +1819,10 @@
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F16">
         <v>-37.815840299999998</v>
@@ -1564,7 +1834,7 @@
         <v>71</v>
       </c>
       <c r="I16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J16">
         <v>3.5</v>
@@ -1592,10 +1862,10 @@
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F17">
         <v>-37.805473399999997</v>
@@ -1607,7 +1877,7 @@
         <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -1635,10 +1905,10 @@
         <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F18">
         <v>-37.813394000000002</v>
@@ -1650,7 +1920,7 @@
         <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -1678,10 +1948,10 @@
         <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F19">
         <v>-37.814913199999999</v>
@@ -1693,7 +1963,7 @@
         <v>75</v>
       </c>
       <c r="I19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J19">
         <v>3.5</v>
@@ -1721,10 +1991,10 @@
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F20">
         <v>-37.815887199999999</v>
@@ -1736,7 +2006,7 @@
         <v>76</v>
       </c>
       <c r="I20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -1764,10 +2034,10 @@
         <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F21">
         <v>-37.816189100000003</v>
@@ -1779,7 +2049,7 @@
         <v>77</v>
       </c>
       <c r="I21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -1807,10 +2077,10 @@
         <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F22">
         <v>-37.805464999999998</v>
@@ -1822,7 +2092,7 @@
         <v>72</v>
       </c>
       <c r="I22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J22">
         <v>3.5</v>
@@ -1850,10 +2120,10 @@
         <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F23">
         <v>-37.8063845</v>
@@ -1865,7 +2135,7 @@
         <v>78</v>
       </c>
       <c r="I23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J23">
         <v>3.5</v>
@@ -1893,10 +2163,10 @@
         <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F24">
         <v>-37.795028600000002</v>
@@ -1908,7 +2178,7 @@
         <v>79</v>
       </c>
       <c r="I24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J24">
         <v>3.5</v>
@@ -1936,10 +2206,10 @@
         <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F25">
         <v>-37.8136394</v>
@@ -1951,7 +2221,7 @@
         <v>80</v>
       </c>
       <c r="I25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J25">
         <v>3.5</v>
@@ -1979,10 +2249,10 @@
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F26">
         <v>-37.864322399999999</v>
@@ -1994,7 +2264,7 @@
         <v>81</v>
       </c>
       <c r="I26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J26">
         <v>2.5</v>
@@ -2022,10 +2292,10 @@
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F27">
         <v>-37.849426999999999</v>
@@ -2037,7 +2307,7 @@
         <v>83</v>
       </c>
       <c r="I27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J27">
         <v>3.5</v>
@@ -2065,10 +2335,10 @@
         <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F28">
         <v>-37.810980200000003</v>
@@ -2080,7 +2350,7 @@
         <v>84</v>
       </c>
       <c r="I28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J28">
         <v>3</v>
@@ -2108,10 +2378,10 @@
         <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F29">
         <v>-37.816451299999997</v>
@@ -2123,7 +2393,7 @@
         <v>85</v>
       </c>
       <c r="I29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J29">
         <v>3.5</v>
@@ -2151,10 +2421,10 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F30">
         <v>-37.788539800000002</v>
@@ -2166,7 +2436,7 @@
         <v>86</v>
       </c>
       <c r="I30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2194,10 +2464,10 @@
         <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F31">
         <v>-37.813554099999998</v>
@@ -2209,7 +2479,7 @@
         <v>87</v>
       </c>
       <c r="I31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J31">
         <v>5</v>
@@ -2237,10 +2507,10 @@
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F32">
         <v>-37.810779599999996</v>
@@ -2252,7 +2522,7 @@
         <v>88</v>
       </c>
       <c r="I32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -2280,10 +2550,10 @@
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F33">
         <v>-37.8150555</v>
@@ -2295,7 +2565,7 @@
         <v>89</v>
       </c>
       <c r="I33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -2323,10 +2593,10 @@
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F34">
         <v>-37.815333000000003</v>
@@ -2338,7 +2608,7 @@
         <v>90</v>
       </c>
       <c r="I34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J34">
         <v>4</v>
@@ -2366,10 +2636,10 @@
         <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35">
         <v>-37.815766099999998</v>
@@ -2381,7 +2651,7 @@
         <v>92</v>
       </c>
       <c r="I35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J35">
         <v>3.5</v>
@@ -2409,10 +2679,10 @@
         <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E36" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F36">
         <v>-37.812815000000001</v>
@@ -2424,7 +2694,7 @@
         <v>93</v>
       </c>
       <c r="I36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J36">
         <v>2.5</v>
@@ -2452,10 +2722,10 @@
         <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37">
         <v>-37.815731999999997</v>
@@ -2467,7 +2737,7 @@
         <v>94</v>
       </c>
       <c r="I37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2495,10 +2765,10 @@
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F38">
         <v>-37.814254800000001</v>
@@ -2510,7 +2780,7 @@
         <v>96</v>
       </c>
       <c r="I38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J38">
         <v>4.5</v>
@@ -2528,20 +2798,20 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" s="1">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
         <v>151</v>
       </c>
-      <c r="B39" s="1">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" t="s">
         <v>152</v>
-      </c>
-      <c r="D39" t="s">
-        <v>142</v>
-      </c>
-      <c r="E39" t="s">
-        <v>153</v>
       </c>
       <c r="F39">
         <v>-37.811877199999998</v>
@@ -2550,10 +2820,10 @@
         <v>144.96924580000001</v>
       </c>
       <c r="H39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J39">
         <v>5</v>
@@ -2567,6 +2837,1164 @@
       <c r="M39" s="1">
         <f t="shared" si="1"/>
         <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="1">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40">
+        <v>-37.809154200000002</v>
+      </c>
+      <c r="G40">
+        <v>144.96813230000001</v>
+      </c>
+      <c r="H40" t="s">
+        <v>157</v>
+      </c>
+      <c r="I40" t="s">
+        <v>147</v>
+      </c>
+      <c r="J40">
+        <v>3</v>
+      </c>
+      <c r="K40">
+        <v>85</v>
+      </c>
+      <c r="L40">
+        <v>85</v>
+      </c>
+      <c r="M40" s="1">
+        <f t="shared" si="1"/>
+        <v>82.828282828282823</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>158</v>
+      </c>
+      <c r="B41" s="1">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="C41" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41">
+        <v>-37.811734999999999</v>
+      </c>
+      <c r="G41">
+        <v>144.96680939999999</v>
+      </c>
+      <c r="H41" t="s">
+        <v>160</v>
+      </c>
+      <c r="I41" t="s">
+        <v>161</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>88</v>
+      </c>
+      <c r="L41">
+        <v>80</v>
+      </c>
+      <c r="M41" s="1">
+        <f t="shared" si="1"/>
+        <v>84.646464646464651</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="1">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" t="s">
+        <v>163</v>
+      </c>
+      <c r="F42">
+        <v>-37.812011900000002</v>
+      </c>
+      <c r="G42">
+        <v>144.96738099999999</v>
+      </c>
+      <c r="H42" t="s">
+        <v>164</v>
+      </c>
+      <c r="I42" t="s">
+        <v>161</v>
+      </c>
+      <c r="J42">
+        <v>1.5</v>
+      </c>
+      <c r="K42">
+        <v>85</v>
+      </c>
+      <c r="L42">
+        <v>82</v>
+      </c>
+      <c r="M42" s="1">
+        <f t="shared" si="1"/>
+        <v>83.131313131313135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="1">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="C43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" t="s">
+        <v>166</v>
+      </c>
+      <c r="F43">
+        <v>-37.812676600000003</v>
+      </c>
+      <c r="G43">
+        <v>144.9683005</v>
+      </c>
+      <c r="H43" t="s">
+        <v>167</v>
+      </c>
+      <c r="I43" t="s">
+        <v>161</v>
+      </c>
+      <c r="J43">
+        <v>1.5</v>
+      </c>
+      <c r="K43">
+        <v>80</v>
+      </c>
+      <c r="L43">
+        <v>80</v>
+      </c>
+      <c r="M43" s="1">
+        <f t="shared" si="1"/>
+        <v>79.292929292929287</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>168</v>
+      </c>
+      <c r="B44" s="1">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" t="s">
+        <v>170</v>
+      </c>
+      <c r="F44">
+        <v>-37.8119345</v>
+      </c>
+      <c r="G44">
+        <v>144.9675737</v>
+      </c>
+      <c r="H44" t="s">
+        <v>171</v>
+      </c>
+      <c r="I44" t="s">
+        <v>161</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44">
+        <v>82</v>
+      </c>
+      <c r="L44">
+        <v>83</v>
+      </c>
+      <c r="M44" s="1">
+        <f t="shared" si="1"/>
+        <v>81.212121212121218</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>172</v>
+      </c>
+      <c r="B45" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" t="s">
+        <v>174</v>
+      </c>
+      <c r="F45">
+        <v>-37.8119345</v>
+      </c>
+      <c r="G45">
+        <v>144.9675737</v>
+      </c>
+      <c r="H45" t="s">
+        <v>175</v>
+      </c>
+      <c r="I45" t="s">
+        <v>161</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45">
+        <v>85</v>
+      </c>
+      <c r="L45">
+        <v>85</v>
+      </c>
+      <c r="M45" s="1">
+        <f t="shared" si="1"/>
+        <v>83.838383838383834</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" s="1">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="C46" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" t="s">
+        <v>177</v>
+      </c>
+      <c r="F46">
+        <v>-37.812353999999999</v>
+      </c>
+      <c r="G46">
+        <v>144.9566317</v>
+      </c>
+      <c r="H46" t="s">
+        <v>178</v>
+      </c>
+      <c r="I46" t="s">
+        <v>161</v>
+      </c>
+      <c r="J46">
+        <v>3</v>
+      </c>
+      <c r="K46">
+        <v>88</v>
+      </c>
+      <c r="L46">
+        <v>86</v>
+      </c>
+      <c r="M46" s="1">
+        <f t="shared" si="1"/>
+        <v>85.050505050505052</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>179</v>
+      </c>
+      <c r="B47" s="1">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C47" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" t="s">
+        <v>180</v>
+      </c>
+      <c r="F47">
+        <v>-37.816072499999997</v>
+      </c>
+      <c r="G47">
+        <v>144.96819170000001</v>
+      </c>
+      <c r="H47" t="s">
+        <v>182</v>
+      </c>
+      <c r="I47" t="s">
+        <v>181</v>
+      </c>
+      <c r="J47">
+        <v>1.5</v>
+      </c>
+      <c r="K47">
+        <v>87</v>
+      </c>
+      <c r="L47">
+        <v>87</v>
+      </c>
+      <c r="M47" s="1">
+        <f t="shared" si="1"/>
+        <v>86.36363636363636</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>183</v>
+      </c>
+      <c r="B48" s="1">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C48" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" t="s">
+        <v>142</v>
+      </c>
+      <c r="E48" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48">
+        <v>-37.814897799999997</v>
+      </c>
+      <c r="G48">
+        <v>144.9725894</v>
+      </c>
+      <c r="H48" t="s">
+        <v>185</v>
+      </c>
+      <c r="I48" t="s">
+        <v>181</v>
+      </c>
+      <c r="J48">
+        <v>1.5</v>
+      </c>
+      <c r="K48">
+        <v>87</v>
+      </c>
+      <c r="L48">
+        <v>87</v>
+      </c>
+      <c r="M48" s="1">
+        <f t="shared" si="1"/>
+        <v>86.36363636363636</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="1">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
+        <v>142</v>
+      </c>
+      <c r="E49" t="s">
+        <v>187</v>
+      </c>
+      <c r="F49">
+        <v>-37.815413200000002</v>
+      </c>
+      <c r="G49">
+        <v>144.97062080000001</v>
+      </c>
+      <c r="H49" t="s">
+        <v>189</v>
+      </c>
+      <c r="I49" t="s">
+        <v>188</v>
+      </c>
+      <c r="J49">
+        <v>1.5</v>
+      </c>
+      <c r="K49">
+        <v>87</v>
+      </c>
+      <c r="L49">
+        <v>86</v>
+      </c>
+      <c r="M49" s="1">
+        <f t="shared" si="1"/>
+        <v>85.959595959595958</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="1">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="C50" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" t="s">
+        <v>141</v>
+      </c>
+      <c r="E50" t="s">
+        <v>191</v>
+      </c>
+      <c r="F50">
+        <v>-37.815526699999999</v>
+      </c>
+      <c r="G50">
+        <v>144.96986010000001</v>
+      </c>
+      <c r="H50" t="s">
+        <v>192</v>
+      </c>
+      <c r="I50" t="s">
+        <v>147</v>
+      </c>
+      <c r="J50">
+        <v>3</v>
+      </c>
+      <c r="K50">
+        <v>85</v>
+      </c>
+      <c r="L50">
+        <v>82</v>
+      </c>
+      <c r="M50" s="1">
+        <f t="shared" si="1"/>
+        <v>81.616161616161619</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="1">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="C51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" t="s">
+        <v>194</v>
+      </c>
+      <c r="F51">
+        <v>-37.815948900000002</v>
+      </c>
+      <c r="G51">
+        <v>144.9682032</v>
+      </c>
+      <c r="H51" t="s">
+        <v>195</v>
+      </c>
+      <c r="I51" t="s">
+        <v>147</v>
+      </c>
+      <c r="J51">
+        <v>3</v>
+      </c>
+      <c r="K51">
+        <v>86</v>
+      </c>
+      <c r="L51">
+        <v>83</v>
+      </c>
+      <c r="M51" s="1">
+        <f t="shared" si="1"/>
+        <v>82.62626262626263</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>196</v>
+      </c>
+      <c r="B52" s="1">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" t="s">
+        <v>197</v>
+      </c>
+      <c r="F52">
+        <v>-37.814322799999999</v>
+      </c>
+      <c r="G52">
+        <v>144.96144169999999</v>
+      </c>
+      <c r="H52" t="s">
+        <v>198</v>
+      </c>
+      <c r="I52" t="s">
+        <v>181</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52">
+        <v>90</v>
+      </c>
+      <c r="L52">
+        <v>87</v>
+      </c>
+      <c r="M52" s="1">
+        <f t="shared" si="1"/>
+        <v>87.676767676767682</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>199</v>
+      </c>
+      <c r="B53" s="1">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="C53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" t="s">
+        <v>200</v>
+      </c>
+      <c r="F53">
+        <v>-37.815802300000001</v>
+      </c>
+      <c r="G53">
+        <v>144.96885420000001</v>
+      </c>
+      <c r="H53" t="s">
+        <v>201</v>
+      </c>
+      <c r="I53" t="s">
+        <v>149</v>
+      </c>
+      <c r="J53">
+        <v>3.5</v>
+      </c>
+      <c r="K53">
+        <v>90</v>
+      </c>
+      <c r="L53">
+        <v>90</v>
+      </c>
+      <c r="M53" s="1">
+        <f t="shared" si="1"/>
+        <v>87.37373737373737</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>205</v>
+      </c>
+      <c r="B54" s="1">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C54" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" t="s">
+        <v>202</v>
+      </c>
+      <c r="F54">
+        <v>-37.815802300000001</v>
+      </c>
+      <c r="G54">
+        <v>144.96885420000001</v>
+      </c>
+      <c r="H54" t="s">
+        <v>204</v>
+      </c>
+      <c r="I54" t="s">
+        <v>203</v>
+      </c>
+      <c r="J54">
+        <v>4</v>
+      </c>
+      <c r="K54">
+        <v>90</v>
+      </c>
+      <c r="L54">
+        <v>88</v>
+      </c>
+      <c r="M54" s="1">
+        <f t="shared" si="1"/>
+        <v>86.060606060606062</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" s="1">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" t="s">
+        <v>142</v>
+      </c>
+      <c r="E55" t="s">
+        <v>208</v>
+      </c>
+      <c r="F55">
+        <v>-37.812705399999999</v>
+      </c>
+      <c r="G55">
+        <v>144.96561869999999</v>
+      </c>
+      <c r="H55" t="s">
+        <v>207</v>
+      </c>
+      <c r="I55" t="s">
+        <v>203</v>
+      </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
+      <c r="K55">
+        <v>92</v>
+      </c>
+      <c r="L55">
+        <v>89</v>
+      </c>
+      <c r="M55" s="1">
+        <f t="shared" si="1"/>
+        <v>87.676767676767682</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>209</v>
+      </c>
+      <c r="B56" s="1">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="C56" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" t="s">
+        <v>144</v>
+      </c>
+      <c r="E56" t="s">
+        <v>211</v>
+      </c>
+      <c r="F56">
+        <v>-37.8152665</v>
+      </c>
+      <c r="G56">
+        <v>144.96972099999999</v>
+      </c>
+      <c r="H56" t="s">
+        <v>210</v>
+      </c>
+      <c r="I56" t="s">
+        <v>147</v>
+      </c>
+      <c r="J56">
+        <v>3</v>
+      </c>
+      <c r="K56">
+        <v>90</v>
+      </c>
+      <c r="L56">
+        <v>94</v>
+      </c>
+      <c r="M56" s="1">
+        <f t="shared" si="1"/>
+        <v>89.494949494949495</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>213</v>
+      </c>
+      <c r="B57" s="1">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="C57" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57" t="s">
+        <v>142</v>
+      </c>
+      <c r="E57" t="s">
+        <v>214</v>
+      </c>
+      <c r="F57">
+        <v>-37.812956300000003</v>
+      </c>
+      <c r="G57">
+        <v>144.96285639999999</v>
+      </c>
+      <c r="H57" t="s">
+        <v>212</v>
+      </c>
+      <c r="I57" t="s">
+        <v>203</v>
+      </c>
+      <c r="J57">
+        <v>2.5</v>
+      </c>
+      <c r="K57">
+        <v>87</v>
+      </c>
+      <c r="L57">
+        <v>95</v>
+      </c>
+      <c r="M57" s="1">
+        <f t="shared" si="1"/>
+        <v>88.585858585858588</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>215</v>
+      </c>
+      <c r="B58" s="1">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="C58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" t="s">
+        <v>142</v>
+      </c>
+      <c r="E58" t="s">
+        <v>216</v>
+      </c>
+      <c r="F58">
+        <v>-37.813351599999997</v>
+      </c>
+      <c r="G58">
+        <v>144.97089500000001</v>
+      </c>
+      <c r="H58" t="s">
+        <v>217</v>
+      </c>
+      <c r="I58" t="s">
+        <v>218</v>
+      </c>
+      <c r="J58">
+        <v>2.5</v>
+      </c>
+      <c r="K58">
+        <v>94</v>
+      </c>
+      <c r="L58">
+        <v>93</v>
+      </c>
+      <c r="M58" s="1">
+        <f t="shared" si="1"/>
+        <v>92.020202020202021</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>219</v>
+      </c>
+      <c r="B59" s="1">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="C59" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" t="s">
+        <v>141</v>
+      </c>
+      <c r="E59" t="s">
+        <v>220</v>
+      </c>
+      <c r="F59">
+        <v>-37.812942700000001</v>
+      </c>
+      <c r="G59">
+        <v>144.9713271</v>
+      </c>
+      <c r="H59" t="s">
+        <v>221</v>
+      </c>
+      <c r="I59" t="s">
+        <v>218</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="K59">
+        <v>87</v>
+      </c>
+      <c r="L59">
+        <v>85</v>
+      </c>
+      <c r="M59" s="1">
+        <f t="shared" si="1"/>
+        <v>85.050505050505052</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>222</v>
+      </c>
+      <c r="B60" s="1">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="C60" t="s">
+        <v>223</v>
+      </c>
+      <c r="D60" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" t="s">
+        <v>225</v>
+      </c>
+      <c r="F60">
+        <v>-37.812434000000003</v>
+      </c>
+      <c r="G60">
+        <v>144.97216280000001</v>
+      </c>
+      <c r="H60" t="s">
+        <v>224</v>
+      </c>
+      <c r="I60" t="s">
+        <v>218</v>
+      </c>
+      <c r="J60">
+        <v>2</v>
+      </c>
+      <c r="K60">
+        <v>89</v>
+      </c>
+      <c r="L60">
+        <v>90</v>
+      </c>
+      <c r="M60" s="1">
+        <f t="shared" si="1"/>
+        <v>88.282828282828291</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>226</v>
+      </c>
+      <c r="B61" s="1">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="C61" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" t="s">
+        <v>142</v>
+      </c>
+      <c r="E61" t="s">
+        <v>227</v>
+      </c>
+      <c r="F61">
+        <v>-37.811082300000002</v>
+      </c>
+      <c r="G61">
+        <v>144.97117950000001</v>
+      </c>
+      <c r="H61" t="s">
+        <v>229</v>
+      </c>
+      <c r="I61" t="s">
+        <v>228</v>
+      </c>
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="K61">
+        <v>93</v>
+      </c>
+      <c r="L61">
+        <v>90</v>
+      </c>
+      <c r="M61" s="1">
+        <f t="shared" si="1"/>
+        <v>90.707070707070699</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>231</v>
+      </c>
+      <c r="B62" s="1">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="C62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" t="s">
+        <v>144</v>
+      </c>
+      <c r="E62" t="s">
+        <v>232</v>
+      </c>
+      <c r="F62">
+        <v>-37.8092483</v>
+      </c>
+      <c r="G62">
+        <v>144.96140410000001</v>
+      </c>
+      <c r="H62" t="s">
+        <v>230</v>
+      </c>
+      <c r="J62">
+        <v>3</v>
+      </c>
+      <c r="K62">
+        <v>88</v>
+      </c>
+      <c r="L62">
+        <v>85</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="1"/>
+        <v>84.646464646464651</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>233</v>
+      </c>
+      <c r="B63" s="1">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="C63" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" t="s">
+        <v>144</v>
+      </c>
+      <c r="E63" t="s">
+        <v>234</v>
+      </c>
+      <c r="F63">
+        <v>-37.806408599999997</v>
+      </c>
+      <c r="G63">
+        <v>144.9628505</v>
+      </c>
+      <c r="H63" t="s">
+        <v>235</v>
+      </c>
+      <c r="I63" t="s">
+        <v>228</v>
+      </c>
+      <c r="J63">
+        <v>3</v>
+      </c>
+      <c r="K63">
+        <v>88</v>
+      </c>
+      <c r="L63">
+        <v>87</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="1"/>
+        <v>85.454545454545453</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>236</v>
+      </c>
+      <c r="B64" s="1">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="C64" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" t="s">
+        <v>142</v>
+      </c>
+      <c r="E64" t="s">
+        <v>237</v>
+      </c>
+      <c r="F64">
+        <v>-37.848519899999999</v>
+      </c>
+      <c r="G64">
+        <v>144.99952830000001</v>
+      </c>
+      <c r="H64" t="s">
+        <v>238</v>
+      </c>
+      <c r="I64" t="s">
+        <v>203</v>
+      </c>
+      <c r="J64">
+        <v>2.5</v>
+      </c>
+      <c r="K64">
+        <v>85</v>
+      </c>
+      <c r="L64">
+        <v>85</v>
+      </c>
+      <c r="M64" s="1">
+        <f t="shared" si="1"/>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>239</v>
+      </c>
+      <c r="B65" s="1">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" t="s">
+        <v>142</v>
+      </c>
+      <c r="E65" t="s">
+        <v>240</v>
+      </c>
+      <c r="F65">
+        <v>-37.806317399999998</v>
+      </c>
+      <c r="G65">
+        <v>144.9638851</v>
+      </c>
+      <c r="H65" t="s">
+        <v>241</v>
+      </c>
+      <c r="I65" t="s">
+        <v>188</v>
+      </c>
+      <c r="J65">
+        <v>3</v>
+      </c>
+      <c r="K65">
+        <v>90</v>
+      </c>
+      <c r="L65">
+        <v>87</v>
+      </c>
+      <c r="M65" s="1">
+        <f t="shared" si="1"/>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>242</v>
+      </c>
+      <c r="B66" s="1">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C66" t="s">
+        <v>30</v>
+      </c>
+      <c r="D66" t="s">
+        <v>142</v>
+      </c>
+      <c r="E66" t="s">
+        <v>243</v>
+      </c>
+      <c r="F66">
+        <v>-37.813313899999997</v>
+      </c>
+      <c r="G66">
+        <v>144.9703523</v>
+      </c>
+      <c r="H66" t="s">
+        <v>244</v>
+      </c>
+      <c r="I66" t="s">
+        <v>188</v>
+      </c>
+      <c r="J66">
+        <v>3</v>
+      </c>
+      <c r="K66">
+        <v>88</v>
+      </c>
+      <c r="L66">
+        <v>88</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" si="1"/>
+        <v>85.858585858585855</v>
       </c>
     </row>
   </sheetData>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="572" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{903A2D98-9FBF-4658-A2B7-AEDDC78ABB62}"/>
+  <xr:revisionPtr revIDLastSave="598" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E486975A-AA51-4B99-BEA9-C03DEBD86B8D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="246">
   <si>
     <t>San Telmo</t>
   </si>
@@ -632,9 +632,6 @@
     <t>Unbelievable pastries, pandan croissant is a must. Also in South Melbourne Market</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/dpCG4735kN8cPFD86</t>
-  </si>
-  <si>
     <t>Apollo Inn</t>
   </si>
   <si>
@@ -728,9 +725,6 @@
     <t>https://maps.app.goo.gl/TL8r1t6cWu3DXyjFA</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/1R5LNXnBeD22U3Ef9</t>
-  </si>
-  <si>
     <t>Roccos Bologna Discoteca</t>
   </si>
   <si>
@@ -774,6 +768,12 @@
   </si>
   <si>
     <t>Plenty of tasty  meat and sushi. Very cool décor</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/E3Gk3gQcoFKNqNC89</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5iN2mPvrVtyn3HbP8</t>
   </si>
 </sst>
 </file>
@@ -827,6 +827,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1154,9 +1158,9 @@
     <col min="3" max="3" width="12.9296875" customWidth="1"/>
     <col min="4" max="4" width="14.19921875" customWidth="1"/>
     <col min="5" max="5" width="66.3984375" customWidth="1"/>
-    <col min="6" max="6" width="12.9296875" customWidth="1"/>
-    <col min="7" max="7" width="17.265625" customWidth="1"/>
-    <col min="8" max="8" width="29.19921875" customWidth="1"/>
+    <col min="6" max="6" width="15.86328125" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
+    <col min="8" max="8" width="66.33203125" customWidth="1"/>
     <col min="9" max="9" width="11.59765625" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="10.06640625" customWidth="1"/>
@@ -1779,7 +1783,7 @@
         <v>141</v>
       </c>
       <c r="E15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F15">
         <v>-37.815804300000003</v>
@@ -2857,10 +2861,10 @@
         <v>156</v>
       </c>
       <c r="F40">
-        <v>-37.809154200000002</v>
+        <v>-37.810694051619983</v>
       </c>
       <c r="G40">
-        <v>144.96813230000001</v>
+        <v>144.97167465163011</v>
       </c>
       <c r="H40" t="s">
         <v>157</v>
@@ -2900,10 +2904,10 @@
         <v>159</v>
       </c>
       <c r="F41">
-        <v>-37.811734999999999</v>
+        <v>-37.812269667878702</v>
       </c>
       <c r="G41">
-        <v>144.96680939999999</v>
+        <v>144.96815321783711</v>
       </c>
       <c r="H41" t="s">
         <v>160</v>
@@ -2943,10 +2947,10 @@
         <v>163</v>
       </c>
       <c r="F42">
-        <v>-37.812011900000002</v>
+        <v>-37.812341042647361</v>
       </c>
       <c r="G42">
-        <v>144.96738099999999</v>
+        <v>144.96809114866701</v>
       </c>
       <c r="H42" t="s">
         <v>164</v>
@@ -2986,10 +2990,10 @@
         <v>166</v>
       </c>
       <c r="F43">
-        <v>-37.812676600000003</v>
+        <v>-37.812580229340412</v>
       </c>
       <c r="G43">
-        <v>144.9683005</v>
+        <v>144.9682649423624</v>
       </c>
       <c r="H43" t="s">
         <v>167</v>
@@ -3029,10 +3033,10 @@
         <v>170</v>
       </c>
       <c r="F44">
-        <v>-37.8119345</v>
+        <v>-37.811908883160037</v>
       </c>
       <c r="G44">
-        <v>144.9675737</v>
+        <v>144.97015223589139</v>
       </c>
       <c r="H44" t="s">
         <v>171</v>
@@ -3072,10 +3076,10 @@
         <v>174</v>
       </c>
       <c r="F45">
-        <v>-37.8119345</v>
+        <v>-37.811747395459307</v>
       </c>
       <c r="G45">
-        <v>144.9675737</v>
+        <v>144.96691968394649</v>
       </c>
       <c r="H45" t="s">
         <v>175</v>
@@ -3115,10 +3119,10 @@
         <v>177</v>
       </c>
       <c r="F46">
-        <v>-37.812353999999999</v>
+        <v>-37.812221057004543</v>
       </c>
       <c r="G46">
-        <v>144.9566317</v>
+        <v>144.96121193018951</v>
       </c>
       <c r="H46" t="s">
         <v>178</v>
@@ -3158,10 +3162,10 @@
         <v>180</v>
       </c>
       <c r="F47">
-        <v>-37.816072499999997</v>
+        <v>-37.815833570942573</v>
       </c>
       <c r="G47">
-        <v>144.96819170000001</v>
+        <v>144.9721335444238</v>
       </c>
       <c r="H47" t="s">
         <v>182</v>
@@ -3201,10 +3205,10 @@
         <v>184</v>
       </c>
       <c r="F48">
-        <v>-37.814897799999997</v>
+        <v>-37.814840179653331</v>
       </c>
       <c r="G48">
-        <v>144.9725894</v>
+        <v>144.97286169729369</v>
       </c>
       <c r="H48" t="s">
         <v>185</v>
@@ -3244,10 +3248,10 @@
         <v>187</v>
       </c>
       <c r="F49">
-        <v>-37.815413200000002</v>
+        <v>-37.815376138728993</v>
       </c>
       <c r="G49">
-        <v>144.97062080000001</v>
+        <v>144.97086521489209</v>
       </c>
       <c r="H49" t="s">
         <v>189</v>
@@ -3287,10 +3291,10 @@
         <v>191</v>
       </c>
       <c r="F50">
-        <v>-37.815526699999999</v>
+        <v>-37.815526962377618</v>
       </c>
       <c r="G50">
-        <v>144.96986010000001</v>
+        <v>144.97034542337241</v>
       </c>
       <c r="H50" t="s">
         <v>192</v>
@@ -3330,10 +3334,10 @@
         <v>194</v>
       </c>
       <c r="F51">
-        <v>-37.815948900000002</v>
+        <v>-37.815972279280103</v>
       </c>
       <c r="G51">
-        <v>144.9682032</v>
+        <v>144.9684197724155</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -3373,13 +3377,13 @@
         <v>197</v>
       </c>
       <c r="F52">
-        <v>-37.814322799999999</v>
+        <v>-37.814588112911387</v>
       </c>
       <c r="G52">
-        <v>144.96144169999999</v>
+        <v>144.96365937652169</v>
       </c>
       <c r="H52" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="I52" t="s">
         <v>181</v>
@@ -3400,7 +3404,7 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B53" s="1">
         <f t="shared" si="0"/>
@@ -3413,16 +3417,16 @@
         <v>142</v>
       </c>
       <c r="E53" t="s">
+        <v>199</v>
+      </c>
+      <c r="F53">
+        <v>-37.815954257806567</v>
+      </c>
+      <c r="G53">
+        <v>144.968990798693</v>
+      </c>
+      <c r="H53" t="s">
         <v>200</v>
-      </c>
-      <c r="F53">
-        <v>-37.815802300000001</v>
-      </c>
-      <c r="G53">
-        <v>144.96885420000001</v>
-      </c>
-      <c r="H53" t="s">
-        <v>201</v>
       </c>
       <c r="I53" t="s">
         <v>149</v>
@@ -3443,7 +3447,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B54" s="1">
         <f t="shared" si="0"/>
@@ -3456,19 +3460,19 @@
         <v>142</v>
       </c>
       <c r="E54" t="s">
+        <v>201</v>
+      </c>
+      <c r="F54">
+        <v>-37.815994516953609</v>
+      </c>
+      <c r="G54">
+        <v>144.96939447113971</v>
+      </c>
+      <c r="H54" t="s">
+        <v>203</v>
+      </c>
+      <c r="I54" t="s">
         <v>202</v>
-      </c>
-      <c r="F54">
-        <v>-37.815802300000001</v>
-      </c>
-      <c r="G54">
-        <v>144.96885420000001</v>
-      </c>
-      <c r="H54" t="s">
-        <v>204</v>
-      </c>
-      <c r="I54" t="s">
-        <v>203</v>
       </c>
       <c r="J54">
         <v>4</v>
@@ -3486,7 +3490,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B55" s="1">
         <f t="shared" si="0"/>
@@ -3499,19 +3503,19 @@
         <v>142</v>
       </c>
       <c r="E55" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F55">
-        <v>-37.812705399999999</v>
+        <v>-37.810065712874973</v>
       </c>
       <c r="G55">
-        <v>144.96561869999999</v>
+        <v>144.96705794313331</v>
       </c>
       <c r="H55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I55" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J55">
         <v>4</v>
@@ -3529,7 +3533,7 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B56" s="1">
         <f t="shared" si="0"/>
@@ -3542,16 +3546,16 @@
         <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F56">
-        <v>-37.8152665</v>
+        <v>-37.815608636812037</v>
       </c>
       <c r="G56">
-        <v>144.96972099999999</v>
+        <v>144.97008073789809</v>
       </c>
       <c r="H56" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I56" t="s">
         <v>147</v>
@@ -3572,7 +3576,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B57" s="1">
         <f t="shared" si="0"/>
@@ -3585,19 +3589,19 @@
         <v>142</v>
       </c>
       <c r="E57" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F57">
-        <v>-37.812956300000003</v>
+        <v>-37.812983327593827</v>
       </c>
       <c r="G57">
-        <v>144.96285639999999</v>
+        <v>144.96302097707229</v>
       </c>
       <c r="H57" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J57">
         <v>2.5</v>
@@ -3615,7 +3619,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B58" s="1">
         <f t="shared" si="0"/>
@@ -3628,19 +3632,19 @@
         <v>142</v>
       </c>
       <c r="E58" t="s">
+        <v>215</v>
+      </c>
+      <c r="F58">
+        <v>-37.812899464861317</v>
+      </c>
+      <c r="G58">
+        <v>144.97170566105669</v>
+      </c>
+      <c r="H58" t="s">
         <v>216</v>
       </c>
-      <c r="F58">
-        <v>-37.813351599999997</v>
-      </c>
-      <c r="G58">
-        <v>144.97089500000001</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
         <v>217</v>
-      </c>
-      <c r="I58" t="s">
-        <v>218</v>
       </c>
       <c r="J58">
         <v>2.5</v>
@@ -3658,7 +3662,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="1">
         <f t="shared" si="0"/>
@@ -3671,19 +3675,19 @@
         <v>141</v>
       </c>
       <c r="E59" t="s">
+        <v>219</v>
+      </c>
+      <c r="F59">
+        <v>-37.812910544245653</v>
+      </c>
+      <c r="G59">
+        <v>144.97162379014179</v>
+      </c>
+      <c r="H59" t="s">
         <v>220</v>
       </c>
-      <c r="F59">
-        <v>-37.812942700000001</v>
-      </c>
-      <c r="G59">
-        <v>144.9713271</v>
-      </c>
-      <c r="H59" t="s">
-        <v>221</v>
-      </c>
       <c r="I59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -3701,32 +3705,32 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
+        <v>221</v>
+      </c>
+      <c r="B60" s="1">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="C60" t="s">
         <v>222</v>
-      </c>
-      <c r="B60" s="1">
-        <f t="shared" si="0"/>
-        <v>88</v>
-      </c>
-      <c r="C60" t="s">
-        <v>223</v>
       </c>
       <c r="D60" t="s">
         <v>141</v>
       </c>
       <c r="E60" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F60">
-        <v>-37.812434000000003</v>
+        <v>-37.812539157599922</v>
       </c>
       <c r="G60">
-        <v>144.97216280000001</v>
+        <v>144.9730431840747</v>
       </c>
       <c r="H60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -3744,7 +3748,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B61" s="1">
         <f t="shared" si="0"/>
@@ -3757,19 +3761,19 @@
         <v>142</v>
       </c>
       <c r="E61" t="s">
+        <v>226</v>
+      </c>
+      <c r="F61">
+        <v>-37.811302624313569</v>
+      </c>
+      <c r="G61">
+        <v>144.9726147223958</v>
+      </c>
+      <c r="H61" t="s">
+        <v>228</v>
+      </c>
+      <c r="I61" t="s">
         <v>227</v>
-      </c>
-      <c r="F61">
-        <v>-37.811082300000002</v>
-      </c>
-      <c r="G61">
-        <v>144.97117950000001</v>
-      </c>
-      <c r="H61" t="s">
-        <v>229</v>
-      </c>
-      <c r="I61" t="s">
-        <v>228</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -3787,7 +3791,7 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B62" s="1">
         <f t="shared" si="0"/>
@@ -3800,16 +3804,19 @@
         <v>144</v>
       </c>
       <c r="E62" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F62">
-        <v>-37.8092483</v>
+        <v>-37.804421549714171</v>
       </c>
       <c r="G62">
-        <v>144.96140410000001</v>
+        <v>144.97481178428711</v>
       </c>
       <c r="H62" t="s">
-        <v>230</v>
+        <v>244</v>
+      </c>
+      <c r="I62" t="s">
+        <v>147</v>
       </c>
       <c r="J62">
         <v>3</v>
@@ -3827,7 +3834,7 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B63" s="1">
         <f t="shared" si="0"/>
@@ -3840,19 +3847,19 @@
         <v>144</v>
       </c>
       <c r="E63" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F63">
-        <v>-37.806408599999997</v>
+        <v>-37.811457071394358</v>
       </c>
       <c r="G63">
-        <v>144.9628505</v>
+        <v>144.98330902173689</v>
       </c>
       <c r="H63" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I63" t="s">
-        <v>228</v>
+        <v>147</v>
       </c>
       <c r="J63">
         <v>3</v>
@@ -3870,7 +3877,7 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B64" s="1">
         <f t="shared" si="0"/>
@@ -3883,19 +3890,19 @@
         <v>142</v>
       </c>
       <c r="E64" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F64">
-        <v>-37.848519899999999</v>
+        <v>-37.829463346138489</v>
       </c>
       <c r="G64">
-        <v>144.99952830000001</v>
+        <v>144.9970989578641</v>
       </c>
       <c r="H64" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I64" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J64">
         <v>2.5</v>
@@ -3913,7 +3920,7 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B65" s="1">
         <f t="shared" si="0"/>
@@ -3926,16 +3933,16 @@
         <v>142</v>
       </c>
       <c r="E65" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F65">
-        <v>-37.806317399999998</v>
+        <v>-37.804407650985858</v>
       </c>
       <c r="G65">
-        <v>144.9638851</v>
+        <v>144.9616612554934</v>
       </c>
       <c r="H65" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I65" t="s">
         <v>188</v>
@@ -3956,7 +3963,7 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B66" s="1">
         <f t="shared" si="0"/>
@@ -3969,16 +3976,16 @@
         <v>142</v>
       </c>
       <c r="E66" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F66">
-        <v>-37.813313899999997</v>
+        <v>-37.813368543612263</v>
       </c>
       <c r="G66">
-        <v>144.9703523</v>
+        <v>144.97026450222339</v>
       </c>
       <c r="H66" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I66" t="s">
         <v>188</v>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="598" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E486975A-AA51-4B99-BEA9-C03DEBD86B8D}"/>
+  <xr:revisionPtr revIDLastSave="636" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C2FFC95-31FF-4EC9-9700-4408356DA2AE}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="255">
   <si>
     <t>San Telmo</t>
   </si>
@@ -774,6 +774,33 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/5iN2mPvrVtyn3HbP8</t>
+  </si>
+  <si>
+    <t>Fonda</t>
+  </si>
+  <si>
+    <t>Popular Mexican chain, great for walk-ins</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/srXKmpAeo2EbHb7N8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FXUZ9Guu15RV4Sof9</t>
+  </si>
+  <si>
+    <t>Really tasty brunch spot. Huge portions</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JNH3vhDcyv2MyYk38</t>
+  </si>
+  <si>
+    <t>Straight Outta Saigon</t>
+  </si>
+  <si>
+    <t>Small trendy modern vietnamese restaurant</t>
+  </si>
+  <si>
+    <t>South of Johnston</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFE0398-5E3D-42F9-829F-76BDA5454F49}">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.19921875" customWidth="1"/>
@@ -1159,7 +1186,7 @@
     <col min="4" max="4" width="14.19921875" customWidth="1"/>
     <col min="5" max="5" width="66.3984375" customWidth="1"/>
     <col min="6" max="6" width="15.86328125" customWidth="1"/>
-    <col min="7" max="7" width="60.6640625" customWidth="1"/>
+    <col min="7" max="7" width="22.3984375" customWidth="1"/>
     <col min="8" max="8" width="66.33203125" customWidth="1"/>
     <col min="9" max="9" width="11.59765625" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
@@ -1214,7 +1241,7 @@
         <v>45</v>
       </c>
       <c r="B2" s="1">
-        <f t="shared" ref="B2:B66" si="0">ROUND(M2,0)</f>
+        <f t="shared" ref="B2:B69" si="0">ROUND(M2,0)</f>
         <v>94</v>
       </c>
       <c r="C2" t="s">
@@ -1248,7 +1275,7 @@
         <v>98</v>
       </c>
       <c r="M2" s="1">
-        <f t="shared" ref="M2:M66" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
+        <f t="shared" ref="M2:M69" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
         <v>93.939393939393938</v>
       </c>
     </row>
@@ -3036,7 +3063,7 @@
         <v>-37.811908883160037</v>
       </c>
       <c r="G44">
-        <v>144.97015223589139</v>
+        <v>144.97015223589099</v>
       </c>
       <c r="H44" t="s">
         <v>171</v>
@@ -4002,6 +4029,135 @@
       <c r="M66" s="1">
         <f t="shared" si="1"/>
         <v>85.858585858585855</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>246</v>
+      </c>
+      <c r="B67" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C67" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" t="s">
+        <v>143</v>
+      </c>
+      <c r="E67" t="s">
+        <v>247</v>
+      </c>
+      <c r="F67">
+        <v>-37.814618478807297</v>
+      </c>
+      <c r="G67">
+        <v>144.97316429335001</v>
+      </c>
+      <c r="H67" t="s">
+        <v>248</v>
+      </c>
+      <c r="I67" t="s">
+        <v>227</v>
+      </c>
+      <c r="J67">
+        <v>2.5</v>
+      </c>
+      <c r="K67">
+        <v>86</v>
+      </c>
+      <c r="L67">
+        <v>84</v>
+      </c>
+      <c r="M67" s="1">
+        <f t="shared" si="1"/>
+        <v>83.535353535353536</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>254</v>
+      </c>
+      <c r="B68" s="1">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C68" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" t="s">
+        <v>142</v>
+      </c>
+      <c r="E68" t="s">
+        <v>250</v>
+      </c>
+      <c r="F68">
+        <v>-37.805952496044398</v>
+      </c>
+      <c r="G68">
+        <v>144.984659053293</v>
+      </c>
+      <c r="H68" t="s">
+        <v>249</v>
+      </c>
+      <c r="I68" t="s">
+        <v>188</v>
+      </c>
+      <c r="J68">
+        <v>2</v>
+      </c>
+      <c r="K68">
+        <v>88</v>
+      </c>
+      <c r="L68">
+        <v>87</v>
+      </c>
+      <c r="M68" s="1">
+        <f t="shared" si="1"/>
+        <v>86.464646464646464</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>252</v>
+      </c>
+      <c r="B69" s="1">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="C69" t="s">
+        <v>43</v>
+      </c>
+      <c r="D69" t="s">
+        <v>141</v>
+      </c>
+      <c r="E69" t="s">
+        <v>253</v>
+      </c>
+      <c r="F69">
+        <v>-37.813026238043904</v>
+      </c>
+      <c r="G69">
+        <v>144.968406913411</v>
+      </c>
+      <c r="H69" t="s">
+        <v>251</v>
+      </c>
+      <c r="I69" t="s">
+        <v>147</v>
+      </c>
+      <c r="J69">
+        <v>3</v>
+      </c>
+      <c r="K69">
+        <v>88</v>
+      </c>
+      <c r="L69">
+        <v>86</v>
+      </c>
+      <c r="M69" s="1">
+        <f t="shared" si="1"/>
+        <v>85.050505050505052</v>
       </c>
     </row>
   </sheetData>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="636" documentId="13_ncr:1_{6B110E32-D919-4039-A06E-9D1CDE8DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C2FFC95-31FF-4EC9-9700-4408356DA2AE}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{CB70CA7D-8960-4D3D-9F79-019573917788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{041CCCED-BA45-4185-9C8F-C26CDD5F6D4E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="271">
   <si>
     <t>San Telmo</t>
   </si>
@@ -801,6 +801,54 @@
   </si>
   <si>
     <t>South of Johnston</t>
+  </si>
+  <si>
+    <t>The Builders Arms</t>
+  </si>
+  <si>
+    <t>The Gertrude Hotel</t>
+  </si>
+  <si>
+    <t>Lupino</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/qA6ALQLdFss7svub6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3ZwvP93QHRxzjBCj7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ZWvzhb9Uykr9EJdm6</t>
+  </si>
+  <si>
+    <t>Busy bar, great food. Tuesday steak night</t>
+  </si>
+  <si>
+    <t>Decent bar food, good place to meet friends.</t>
+  </si>
+  <si>
+    <t>Nice restaurant, probably a bit too fancy for just lunch.</t>
+  </si>
+  <si>
+    <t>Nicos Sandwich Deli</t>
+  </si>
+  <si>
+    <t>Great, fresh sandwiches. Weekdays only</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/hveF9EtL3F7DS3dG9</t>
+  </si>
+  <si>
+    <t>B Churrasco Brazilian BBQ</t>
+  </si>
+  <si>
+    <t>Brazilian</t>
+  </si>
+  <si>
+    <t>All you can eat Brazilian BBQ, unique serice. Loads of meat.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Gz358H4hZYrCA7Qs6</t>
   </si>
 </sst>
 </file>
@@ -854,10 +902,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1177,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFE0398-5E3D-42F9-829F-76BDA5454F49}">
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.19921875" customWidth="1"/>
@@ -1241,7 +1285,7 @@
         <v>45</v>
       </c>
       <c r="B2" s="1">
-        <f t="shared" ref="B2:B69" si="0">ROUND(M2,0)</f>
+        <f t="shared" ref="B2:B74" si="0">ROUND(M2,0)</f>
         <v>94</v>
       </c>
       <c r="C2" t="s">
@@ -1275,7 +1319,7 @@
         <v>98</v>
       </c>
       <c r="M2" s="1">
-        <f t="shared" ref="M2:M69" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
+        <f t="shared" ref="M2:M74" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
         <v>93.939393939393938</v>
       </c>
     </row>
@@ -3834,10 +3878,10 @@
         <v>230</v>
       </c>
       <c r="F62">
-        <v>-37.804421549714171</v>
+        <v>-37.805274157822701</v>
       </c>
       <c r="G62">
-        <v>144.97481178428711</v>
+        <v>144.97502770103799</v>
       </c>
       <c r="H62" t="s">
         <v>244</v>
@@ -4158,6 +4202,221 @@
       <c r="M69" s="1">
         <f t="shared" si="1"/>
         <v>85.050505050505052</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>255</v>
+      </c>
+      <c r="B70" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C70" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70" t="s">
+        <v>142</v>
+      </c>
+      <c r="E70" t="s">
+        <v>261</v>
+      </c>
+      <c r="F70">
+        <v>-37.8059369769489</v>
+      </c>
+      <c r="G70">
+        <v>144.98169239010099</v>
+      </c>
+      <c r="H70" t="s">
+        <v>258</v>
+      </c>
+      <c r="I70" t="s">
+        <v>202</v>
+      </c>
+      <c r="J70">
+        <v>2.5</v>
+      </c>
+      <c r="K70">
+        <v>86</v>
+      </c>
+      <c r="L70">
+        <v>85</v>
+      </c>
+      <c r="M70" s="1">
+        <f t="shared" si="1"/>
+        <v>83.939393939393938</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>256</v>
+      </c>
+      <c r="B71" s="1">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C71" t="s">
+        <v>30</v>
+      </c>
+      <c r="D71" t="s">
+        <v>142</v>
+      </c>
+      <c r="E71" t="s">
+        <v>262</v>
+      </c>
+      <c r="F71">
+        <v>-37.806169203803798</v>
+      </c>
+      <c r="G71">
+        <v>144.97923370039601</v>
+      </c>
+      <c r="H71" t="s">
+        <v>259</v>
+      </c>
+      <c r="I71" t="s">
+        <v>202</v>
+      </c>
+      <c r="J71">
+        <v>3</v>
+      </c>
+      <c r="K71">
+        <v>84</v>
+      </c>
+      <c r="L71">
+        <v>83</v>
+      </c>
+      <c r="M71" s="1">
+        <f t="shared" si="1"/>
+        <v>81.414141414141412</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>257</v>
+      </c>
+      <c r="B72" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" t="s">
+        <v>144</v>
+      </c>
+      <c r="E72" t="s">
+        <v>263</v>
+      </c>
+      <c r="F72">
+        <v>-37.812681827366497</v>
+      </c>
+      <c r="G72">
+        <v>144.97233693923599</v>
+      </c>
+      <c r="H72" t="s">
+        <v>260</v>
+      </c>
+      <c r="I72" t="s">
+        <v>147</v>
+      </c>
+      <c r="J72">
+        <v>3.5</v>
+      </c>
+      <c r="K72">
+        <v>87</v>
+      </c>
+      <c r="L72">
+        <v>85</v>
+      </c>
+      <c r="M72" s="1">
+        <f t="shared" si="1"/>
+        <v>83.535353535353536</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>264</v>
+      </c>
+      <c r="B73" s="1">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="C73" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" t="s">
+        <v>142</v>
+      </c>
+      <c r="E73" t="s">
+        <v>265</v>
+      </c>
+      <c r="F73">
+        <v>-37.813540274691697</v>
+      </c>
+      <c r="G73">
+        <v>144.96991551298299</v>
+      </c>
+      <c r="H73" t="s">
+        <v>266</v>
+      </c>
+      <c r="I73" t="s">
+        <v>217</v>
+      </c>
+      <c r="J73">
+        <v>2</v>
+      </c>
+      <c r="K73">
+        <v>88</v>
+      </c>
+      <c r="L73">
+        <v>83</v>
+      </c>
+      <c r="M73" s="1">
+        <f t="shared" si="1"/>
+        <v>84.848484848484844</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>267</v>
+      </c>
+      <c r="B74" s="1">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C74" t="s">
+        <v>268</v>
+      </c>
+      <c r="D74" t="s">
+        <v>143</v>
+      </c>
+      <c r="E74" t="s">
+        <v>269</v>
+      </c>
+      <c r="F74">
+        <v>-37.808710505112401</v>
+      </c>
+      <c r="G74">
+        <v>144.96177636627201</v>
+      </c>
+      <c r="H74" t="s">
+        <v>270</v>
+      </c>
+      <c r="I74" t="s">
+        <v>147</v>
+      </c>
+      <c r="J74">
+        <v>3</v>
+      </c>
+      <c r="K74">
+        <v>87</v>
+      </c>
+      <c r="L74">
+        <v>90</v>
+      </c>
+      <c r="M74" s="1">
+        <f t="shared" si="1"/>
+        <v>86.060606060606062</v>
       </c>
     </row>
   </sheetData>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{CB70CA7D-8960-4D3D-9F79-019573917788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{041CCCED-BA45-4185-9C8F-C26CDD5F6D4E}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{CB70CA7D-8960-4D3D-9F79-019573917788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CEA4FA9-7C9C-4C96-AF12-185872CF2CF6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="299">
   <si>
     <t>San Telmo</t>
   </si>
@@ -152,9 +152,6 @@
     <t>Spanish</t>
   </si>
   <si>
-    <t>Tapas Bar</t>
-  </si>
-  <si>
     <t>Peruvian</t>
   </si>
   <si>
@@ -164,9 +161,6 @@
     <t>Latin American</t>
   </si>
   <si>
-    <t>Japanese Grill</t>
-  </si>
-  <si>
     <t>Vietnamese</t>
   </si>
   <si>
@@ -845,17 +839,107 @@
     <t>Brazilian</t>
   </si>
   <si>
-    <t>All you can eat Brazilian BBQ, unique serice. Loads of meat.</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/Gz358H4hZYrCA7Qs6</t>
+  </si>
+  <si>
+    <t>Reed House</t>
+  </si>
+  <si>
+    <t>English food that isn’t shite. Cool location, solid meal.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wrHNNoXmHybBVwKV8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/iwE5Lkzc5gfjmM2cA</t>
+  </si>
+  <si>
+    <t>Ramen Ippudo</t>
+  </si>
+  <si>
+    <t>Another quality ramen spot, recommended by a local</t>
+  </si>
+  <si>
+    <t>All you can eat Brazilian BBQ, unique service. Loads of meat.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/XYFR8QQzXAbMXEn48</t>
+  </si>
+  <si>
+    <t>Paik's BBQ</t>
+  </si>
+  <si>
+    <t>Chaotic but delicious Korean BBQ place. Highly recommend going with someone who knows what they are doing!</t>
+  </si>
+  <si>
+    <t>No22 Café</t>
+  </si>
+  <si>
+    <t>Cosy Italian foccacia style sandwich shop</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/shV8pM4wb9xiVhkw7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ofXcGwRSxU7Jo1AE9</t>
+  </si>
+  <si>
+    <t>Red Spice Road</t>
+  </si>
+  <si>
+    <t>Another amzaing Asian fusion place with great feed me menus</t>
+  </si>
+  <si>
+    <t>Gimlet</t>
+  </si>
+  <si>
+    <t>High end restaurant, CBD staple. Great for a fancy lunch or special occasion</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/DPWsQiNgU7bb5eTD9</t>
+  </si>
+  <si>
+    <t>Kikanbo</t>
+  </si>
+  <si>
+    <t>Viral ramen spot often with big queues at weekend. Quieter mid-week. Up there with the best ramen in town</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/KPwpM9e245WPsuo76</t>
+  </si>
+  <si>
+    <t>Hopper Joint</t>
+  </si>
+  <si>
+    <t>Sri Lankan</t>
+  </si>
+  <si>
+    <t>Random Sri Lankan joint, meaty, tasty and spicy.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/eLTd4PmXHkZT3bmb9</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Vlado's Charcoal Grill</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/4kYMxa5gFYCMwthWA</t>
+  </si>
+  <si>
+    <t>Steakhouse</t>
+  </si>
+  <si>
+    <t>Iconic steakhouse with unchanged minimal menu for 50 years. Great experience</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -902,6 +986,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1221,81 +1309,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFE0398-5E3D-42F9-829F-76BDA5454F49}">
-  <dimension ref="A1:M74"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:M83"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.19921875" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" customWidth="1"/>
-    <col min="3" max="3" width="12.9296875" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" customWidth="1"/>
-    <col min="5" max="5" width="66.3984375" customWidth="1"/>
-    <col min="6" max="6" width="15.86328125" customWidth="1"/>
-    <col min="7" max="7" width="22.3984375" customWidth="1"/>
-    <col min="8" max="8" width="66.33203125" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.06640625" customWidth="1"/>
-    <col min="12" max="12" width="13.9296875" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1875" customWidth="1"/>
+    <col min="2" max="2" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="12.9375" customWidth="1"/>
+    <col min="4" max="4" width="14.1875" customWidth="1"/>
+    <col min="5" max="5" width="66.375" customWidth="1"/>
+    <col min="6" max="6" width="15.875" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
+    <col min="8" max="8" width="66.3125" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="12.6875" customWidth="1"/>
+    <col min="11" max="11" width="10.0625" customWidth="1"/>
+    <col min="12" max="12" width="13.9375" customWidth="1"/>
+    <col min="13" max="13" width="12.6875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>53</v>
       </c>
-      <c r="J1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1">
-        <f t="shared" ref="B2:B74" si="0">ROUND(M2,0)</f>
+        <f t="shared" ref="B2:B83" si="0">ROUND(M2,0)</f>
         <v>94</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F2">
         <v>-37.819744399999998</v>
@@ -1304,10 +1392,10 @@
         <v>145.00502520000001</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -1319,13 +1407,13 @@
         <v>98</v>
       </c>
       <c r="M2" s="1">
-        <f t="shared" ref="M2:M74" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
+        <f t="shared" ref="M2:M83" si="1">((((3*K2)+(2*L2))-(5*J2))/495)*100</f>
         <v>93.939393939393938</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" s="1">
         <f t="shared" si="0"/>
@@ -1335,10 +1423,10 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F3">
         <v>-37.816214700000003</v>
@@ -1347,10 +1435,10 @@
         <v>144.96879939999999</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1366,9 +1454,9 @@
         <v>92.72727272727272</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
@@ -1378,10 +1466,10 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F4">
         <v>-37.855813300000001</v>
@@ -1390,10 +1478,10 @@
         <v>145.02494609999999</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -1409,7 +1497,7 @@
         <v>93.333333333333329</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1421,10 +1509,10 @@
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F5">
         <v>-37.815699100000003</v>
@@ -1433,10 +1521,10 @@
         <v>144.97141070000001</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J5">
         <v>3.5</v>
@@ -1452,7 +1540,7 @@
         <v>90.808080808080803</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1464,10 +1552,10 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F6">
         <v>-37.812163599999998</v>
@@ -1476,10 +1564,10 @@
         <v>144.97241320000001</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J6">
         <v>4.5</v>
@@ -1495,7 +1583,7 @@
         <v>90.404040404040416</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1507,10 +1595,10 @@
         <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F7">
         <v>-37.816716700000001</v>
@@ -1519,10 +1607,10 @@
         <v>144.96914169999999</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -1538,7 +1626,7 @@
         <v>89.292929292929287</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1550,10 +1638,10 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F8">
         <v>-37.816099999999999</v>
@@ -1562,10 +1650,10 @@
         <v>144.96879939999999</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J8">
         <v>4.5</v>
@@ -1581,7 +1669,7 @@
         <v>89.393939393939391</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1593,10 +1681,10 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F9">
         <v>-37.814523000000001</v>
@@ -1605,10 +1693,10 @@
         <v>144.974164</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J9">
         <v>2.5</v>
@@ -1624,9 +1712,9 @@
         <v>87.777777777777771</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
@@ -1636,10 +1724,10 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F10">
         <v>-37.813552199999997</v>
@@ -1648,10 +1736,10 @@
         <v>144.9619835</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -1667,7 +1755,7 @@
         <v>88.080808080808083</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1679,10 +1767,10 @@
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F11">
         <v>-37.813279100000003</v>
@@ -1691,10 +1779,10 @@
         <v>144.96851409999999</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -1710,9 +1798,9 @@
         <v>87.070707070707059</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
@@ -1722,10 +1810,10 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F12">
         <v>-37.815992799999997</v>
@@ -1734,10 +1822,10 @@
         <v>144.96995380000001</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -1753,7 +1841,7 @@
         <v>86.767676767676775</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -1765,10 +1853,10 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F13">
         <v>-37.8181528</v>
@@ -1777,10 +1865,10 @@
         <v>144.96266199999999</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1796,7 +1884,7 @@
         <v>86.26262626262627</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1805,13 +1893,13 @@
         <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F14">
         <v>-37.813893700000001</v>
@@ -1820,10 +1908,10 @@
         <v>144.96168950000001</v>
       </c>
       <c r="H14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -1839,7 +1927,7 @@
         <v>86.464646464646464</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1848,13 +1936,13 @@
         <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F15">
         <v>-37.815804300000003</v>
@@ -1863,10 +1951,10 @@
         <v>144.97253459999999</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -1882,7 +1970,7 @@
         <v>84.646464646464651</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1891,13 +1979,13 @@
         <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F16">
         <v>-37.815840299999998</v>
@@ -1906,10 +1994,10 @@
         <v>144.9710359</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J16">
         <v>3.5</v>
@@ -1925,7 +2013,7 @@
         <v>84.747474747474755</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1937,10 +2025,10 @@
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F17">
         <v>-37.805473399999997</v>
@@ -1949,10 +2037,10 @@
         <v>144.97585419999999</v>
       </c>
       <c r="H17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -1968,7 +2056,7 @@
         <v>85.050505050505052</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -1980,10 +2068,10 @@
         <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F18">
         <v>-37.813394000000002</v>
@@ -1992,10 +2080,10 @@
         <v>144.9686092</v>
       </c>
       <c r="H18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -2011,7 +2099,7 @@
         <v>85.25252525252526</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2023,10 +2111,10 @@
         <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F19">
         <v>-37.814913199999999</v>
@@ -2035,10 +2123,10 @@
         <v>144.97312289999999</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J19">
         <v>3.5</v>
@@ -2054,7 +2142,7 @@
         <v>85.353535353535349</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -2066,10 +2154,10 @@
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F20">
         <v>-37.815887199999999</v>
@@ -2078,10 +2166,10 @@
         <v>144.96873160000001</v>
       </c>
       <c r="H20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -2097,7 +2185,7 @@
         <v>84.040404040404042</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -2109,10 +2197,10 @@
         <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F21">
         <v>-37.816189100000003</v>
@@ -2121,10 +2209,10 @@
         <v>144.9683115</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -2140,7 +2228,7 @@
         <v>84.242424242424235</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2152,10 +2240,10 @@
         <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F22">
         <v>-37.805464999999998</v>
@@ -2164,10 +2252,10 @@
         <v>144.97589930000001</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J22">
         <v>3.5</v>
@@ -2183,7 +2271,7 @@
         <v>84.343434343434339</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -2192,13 +2280,13 @@
         <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F23">
         <v>-37.8063845</v>
@@ -2207,10 +2295,10 @@
         <v>144.98510970000001</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J23">
         <v>3.5</v>
@@ -2226,7 +2314,7 @@
         <v>82.929292929292927</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -2235,13 +2323,13 @@
         <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F24">
         <v>-37.795028600000002</v>
@@ -2250,10 +2338,10 @@
         <v>144.9792506</v>
       </c>
       <c r="H24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I24" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J24">
         <v>3.5</v>
@@ -2269,7 +2357,7 @@
         <v>83.333333333333343</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2281,10 +2369,10 @@
         <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F25">
         <v>-37.8136394</v>
@@ -2293,10 +2381,10 @@
         <v>144.9733909</v>
       </c>
       <c r="H25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J25">
         <v>3.5</v>
@@ -2312,9 +2400,9 @@
         <v>82.323232323232318</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
@@ -2324,10 +2412,10 @@
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F26">
         <v>-37.864322399999999</v>
@@ -2336,10 +2424,10 @@
         <v>144.98226339999999</v>
       </c>
       <c r="H26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J26">
         <v>2.5</v>
@@ -2355,7 +2443,7 @@
         <v>82.323232323232318</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -2367,10 +2455,10 @@
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E27" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F27">
         <v>-37.849426999999999</v>
@@ -2379,10 +2467,10 @@
         <v>144.99151900000001</v>
       </c>
       <c r="H27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J27">
         <v>3.5</v>
@@ -2398,7 +2486,7 @@
         <v>80.505050505050505</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -2410,10 +2498,10 @@
         <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F28">
         <v>-37.810980200000003</v>
@@ -2422,10 +2510,10 @@
         <v>144.97253789999999</v>
       </c>
       <c r="H28" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J28">
         <v>3</v>
@@ -2441,7 +2529,7 @@
         <v>80.606060606060609</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -2453,10 +2541,10 @@
         <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F29">
         <v>-37.816451299999997</v>
@@ -2465,10 +2553,10 @@
         <v>144.96909969999999</v>
       </c>
       <c r="H29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J29">
         <v>3.5</v>
@@ -2484,22 +2572,22 @@
         <v>81.111111111111114</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F30">
         <v>-37.788539800000002</v>
@@ -2508,10 +2596,10 @@
         <v>144.9318371</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2527,9 +2615,9 @@
         <v>81.212121212121218</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
@@ -2539,10 +2627,10 @@
         <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F31">
         <v>-37.813554099999998</v>
@@ -2551,10 +2639,10 @@
         <v>144.97102520000001</v>
       </c>
       <c r="H31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J31">
         <v>5</v>
@@ -2570,7 +2658,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -2579,13 +2667,13 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F32">
         <v>-37.810779599999996</v>
@@ -2594,10 +2682,10 @@
         <v>144.97079550000001</v>
       </c>
       <c r="H32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I32" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -2613,9 +2701,9 @@
         <v>78.585858585858574</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
@@ -2625,10 +2713,10 @@
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F33">
         <v>-37.8150555</v>
@@ -2637,10 +2725,10 @@
         <v>144.97252929999999</v>
       </c>
       <c r="H33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I33" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -2656,9 +2744,9 @@
         <v>78.98989898989899</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B34" s="1">
         <f t="shared" si="0"/>
@@ -2668,10 +2756,10 @@
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F34">
         <v>-37.815333000000003</v>
@@ -2680,10 +2768,10 @@
         <v>144.96267309999999</v>
       </c>
       <c r="H34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J34">
         <v>4</v>
@@ -2699,7 +2787,7 @@
         <v>78.383838383838395</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -2711,10 +2799,10 @@
         <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E35" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F35">
         <v>-37.815766099999998</v>
@@ -2723,10 +2811,10 @@
         <v>144.96988970000001</v>
       </c>
       <c r="H35" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J35">
         <v>3.5</v>
@@ -2742,7 +2830,7 @@
         <v>76.060606060606062</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -2751,13 +2839,13 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F36">
         <v>-37.812815000000001</v>
@@ -2766,10 +2854,10 @@
         <v>144.97251850000001</v>
       </c>
       <c r="H36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J36">
         <v>2.5</v>
@@ -2785,7 +2873,7 @@
         <v>74.242424242424249</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -2797,10 +2885,10 @@
         <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F37">
         <v>-37.815731999999997</v>
@@ -2809,10 +2897,10 @@
         <v>144.97268800000001</v>
       </c>
       <c r="H37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2828,9 +2916,9 @@
         <v>70.707070707070713</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B38" s="1">
         <f t="shared" si="0"/>
@@ -2840,10 +2928,10 @@
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F38">
         <v>-37.814254800000001</v>
@@ -2852,10 +2940,10 @@
         <v>144.974186</v>
       </c>
       <c r="H38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J38">
         <v>4.5</v>
@@ -2871,22 +2959,22 @@
         <v>62.121212121212125</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
+        <v>148</v>
+      </c>
+      <c r="B39" s="1">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
+        <v>149</v>
+      </c>
+      <c r="D39" t="s">
+        <v>139</v>
+      </c>
+      <c r="E39" t="s">
         <v>150</v>
-      </c>
-      <c r="B39" s="1">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
-        <v>151</v>
-      </c>
-      <c r="D39" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" t="s">
-        <v>152</v>
       </c>
       <c r="F39">
         <v>-37.811877199999998</v>
@@ -2895,10 +2983,10 @@
         <v>144.96924580000001</v>
       </c>
       <c r="H39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I39" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J39">
         <v>5</v>
@@ -2914,9 +3002,9 @@
         <v>86.666666666666671</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B40" s="1">
         <f t="shared" si="0"/>
@@ -2926,10 +3014,10 @@
         <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F40">
         <v>-37.810694051619983</v>
@@ -2938,10 +3026,10 @@
         <v>144.97167465163011</v>
       </c>
       <c r="H40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J40">
         <v>3</v>
@@ -2957,9 +3045,9 @@
         <v>82.828282828282823</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B41" s="1">
         <f t="shared" si="0"/>
@@ -2969,10 +3057,10 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E41" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F41">
         <v>-37.812269667878702</v>
@@ -2981,10 +3069,10 @@
         <v>144.96815321783711</v>
       </c>
       <c r="H41" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I41" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3000,9 +3088,9 @@
         <v>84.646464646464651</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B42" s="1">
         <f t="shared" si="0"/>
@@ -3012,10 +3100,10 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E42" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F42">
         <v>-37.812341042647361</v>
@@ -3024,10 +3112,10 @@
         <v>144.96809114866701</v>
       </c>
       <c r="H42" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I42" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J42">
         <v>1.5</v>
@@ -3043,9 +3131,9 @@
         <v>83.131313131313135</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:13">
       <c r="A43" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B43" s="1">
         <f t="shared" si="0"/>
@@ -3055,10 +3143,10 @@
         <v>33</v>
       </c>
       <c r="D43" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E43" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F43">
         <v>-37.812580229340412</v>
@@ -3067,10 +3155,10 @@
         <v>144.9682649423624</v>
       </c>
       <c r="H43" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I43" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J43">
         <v>1.5</v>
@@ -3086,22 +3174,22 @@
         <v>79.292929292929287</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="1">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D44" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" t="s">
         <v>168</v>
-      </c>
-      <c r="B44" s="1">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="C44" t="s">
-        <v>169</v>
-      </c>
-      <c r="D44" t="s">
-        <v>141</v>
-      </c>
-      <c r="E44" t="s">
-        <v>170</v>
       </c>
       <c r="F44">
         <v>-37.811908883160037</v>
@@ -3110,10 +3198,10 @@
         <v>144.97015223589099</v>
       </c>
       <c r="H44" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J44">
         <v>2</v>
@@ -3129,22 +3217,22 @@
         <v>81.212121212121218</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
+        <v>170</v>
+      </c>
+      <c r="B45" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>171</v>
+      </c>
+      <c r="D45" t="s">
+        <v>139</v>
+      </c>
+      <c r="E45" t="s">
         <v>172</v>
-      </c>
-      <c r="B45" s="1">
-        <f t="shared" si="0"/>
-        <v>84</v>
-      </c>
-      <c r="C45" t="s">
-        <v>173</v>
-      </c>
-      <c r="D45" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" t="s">
-        <v>174</v>
       </c>
       <c r="F45">
         <v>-37.811747395459307</v>
@@ -3153,10 +3241,10 @@
         <v>144.96691968394649</v>
       </c>
       <c r="H45" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I45" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J45">
         <v>2</v>
@@ -3172,9 +3260,9 @@
         <v>83.838383838383834</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B46" s="1">
         <f t="shared" si="0"/>
@@ -3184,10 +3272,10 @@
         <v>33</v>
       </c>
       <c r="D46" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F46">
         <v>-37.812221057004543</v>
@@ -3196,10 +3284,10 @@
         <v>144.96121193018951</v>
       </c>
       <c r="H46" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I46" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J46">
         <v>3</v>
@@ -3215,9 +3303,9 @@
         <v>85.050505050505052</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B47" s="1">
         <f t="shared" si="0"/>
@@ -3227,10 +3315,10 @@
         <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F47">
         <v>-37.815833570942573</v>
@@ -3239,10 +3327,10 @@
         <v>144.9721335444238</v>
       </c>
       <c r="H47" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J47">
         <v>1.5</v>
@@ -3258,9 +3346,9 @@
         <v>86.36363636363636</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B48" s="1">
         <f t="shared" si="0"/>
@@ -3270,10 +3358,10 @@
         <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F48">
         <v>-37.814840179653331</v>
@@ -3282,10 +3370,10 @@
         <v>144.97286169729369</v>
       </c>
       <c r="H48" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I48" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J48">
         <v>1.5</v>
@@ -3301,9 +3389,9 @@
         <v>86.36363636363636</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B49" s="1">
         <f t="shared" si="0"/>
@@ -3313,10 +3401,10 @@
         <v>30</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F49">
         <v>-37.815376138728993</v>
@@ -3325,10 +3413,10 @@
         <v>144.97086521489209</v>
       </c>
       <c r="H49" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I49" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J49">
         <v>1.5</v>
@@ -3344,9 +3432,9 @@
         <v>85.959595959595958</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:13">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B50" s="1">
         <f t="shared" si="0"/>
@@ -3356,10 +3444,10 @@
         <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E50" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F50">
         <v>-37.815526962377618</v>
@@ -3368,10 +3456,10 @@
         <v>144.97034542337241</v>
       </c>
       <c r="H50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J50">
         <v>3</v>
@@ -3387,9 +3475,9 @@
         <v>81.616161616161619</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:13">
       <c r="A51" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B51" s="1">
         <f t="shared" si="0"/>
@@ -3399,10 +3487,10 @@
         <v>29</v>
       </c>
       <c r="D51" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E51" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F51">
         <v>-37.815972279280103</v>
@@ -3411,10 +3499,10 @@
         <v>144.9684197724155</v>
       </c>
       <c r="H51" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I51" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J51">
         <v>3</v>
@@ -3430,9 +3518,9 @@
         <v>82.62626262626263</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:13">
       <c r="A52" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B52" s="1">
         <f t="shared" si="0"/>
@@ -3442,10 +3530,10 @@
         <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E52" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F52">
         <v>-37.814588112911387</v>
@@ -3454,10 +3542,10 @@
         <v>144.96365937652169</v>
       </c>
       <c r="H52" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I52" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J52">
         <v>2</v>
@@ -3473,9 +3561,9 @@
         <v>87.676767676767682</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:13">
       <c r="A53" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B53" s="1">
         <f t="shared" si="0"/>
@@ -3485,10 +3573,10 @@
         <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E53" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F53">
         <v>-37.815954257806567</v>
@@ -3497,10 +3585,10 @@
         <v>144.968990798693</v>
       </c>
       <c r="H53" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I53" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J53">
         <v>3.5</v>
@@ -3516,9 +3604,9 @@
         <v>87.37373737373737</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:13">
       <c r="A54" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B54" s="1">
         <f t="shared" si="0"/>
@@ -3528,10 +3616,10 @@
         <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E54" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F54">
         <v>-37.815994516953609</v>
@@ -3540,10 +3628,10 @@
         <v>144.96939447113971</v>
       </c>
       <c r="H54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I54" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J54">
         <v>4</v>
@@ -3559,9 +3647,9 @@
         <v>86.060606060606062</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:13">
       <c r="A55" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B55" s="1">
         <f t="shared" si="0"/>
@@ -3571,10 +3659,10 @@
         <v>30</v>
       </c>
       <c r="D55" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E55" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F55">
         <v>-37.810065712874973</v>
@@ -3583,10 +3671,10 @@
         <v>144.96705794313331</v>
       </c>
       <c r="H55" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I55" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J55">
         <v>4</v>
@@ -3602,9 +3690,9 @@
         <v>87.676767676767682</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:13">
       <c r="A56" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B56" s="1">
         <f t="shared" si="0"/>
@@ -3614,10 +3702,10 @@
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E56" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F56">
         <v>-37.815608636812037</v>
@@ -3626,10 +3714,10 @@
         <v>144.97008073789809</v>
       </c>
       <c r="H56" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J56">
         <v>3</v>
@@ -3645,9 +3733,9 @@
         <v>89.494949494949495</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:13">
       <c r="A57" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B57" s="1">
         <f t="shared" si="0"/>
@@ -3657,10 +3745,10 @@
         <v>30</v>
       </c>
       <c r="D57" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E57" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F57">
         <v>-37.812983327593827</v>
@@ -3669,10 +3757,10 @@
         <v>144.96302097707229</v>
       </c>
       <c r="H57" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I57" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J57">
         <v>2.5</v>
@@ -3688,9 +3776,9 @@
         <v>88.585858585858588</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:13">
       <c r="A58" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B58" s="1">
         <f t="shared" si="0"/>
@@ -3700,10 +3788,10 @@
         <v>30</v>
       </c>
       <c r="D58" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E58" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F58">
         <v>-37.812899464861317</v>
@@ -3712,10 +3800,10 @@
         <v>144.97170566105669</v>
       </c>
       <c r="H58" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I58" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J58">
         <v>2.5</v>
@@ -3731,9 +3819,9 @@
         <v>92.020202020202021</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:13">
       <c r="A59" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B59" s="1">
         <f t="shared" si="0"/>
@@ -3743,10 +3831,10 @@
         <v>29</v>
       </c>
       <c r="D59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E59" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F59">
         <v>-37.812910544245653</v>
@@ -3755,10 +3843,10 @@
         <v>144.97162379014179</v>
       </c>
       <c r="H59" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I59" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -3774,22 +3862,22 @@
         <v>85.050505050505052</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:13">
       <c r="A60" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B60" s="1">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
       <c r="C60" t="s">
+        <v>220</v>
+      </c>
+      <c r="D60" t="s">
+        <v>139</v>
+      </c>
+      <c r="E60" t="s">
         <v>222</v>
-      </c>
-      <c r="D60" t="s">
-        <v>141</v>
-      </c>
-      <c r="E60" t="s">
-        <v>224</v>
       </c>
       <c r="F60">
         <v>-37.812539157599922</v>
@@ -3798,10 +3886,10 @@
         <v>144.9730431840747</v>
       </c>
       <c r="H60" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I60" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -3817,9 +3905,9 @@
         <v>88.282828282828291</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:13">
       <c r="A61" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B61" s="1">
         <f t="shared" si="0"/>
@@ -3829,10 +3917,10 @@
         <v>30</v>
       </c>
       <c r="D61" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E61" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F61">
         <v>-37.811302624313569</v>
@@ -3841,10 +3929,10 @@
         <v>144.9726147223958</v>
       </c>
       <c r="H61" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I61" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -3860,9 +3948,9 @@
         <v>90.707070707070699</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:13">
       <c r="A62" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B62" s="1">
         <f t="shared" si="0"/>
@@ -3872,10 +3960,10 @@
         <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E62" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F62">
         <v>-37.805274157822701</v>
@@ -3884,10 +3972,10 @@
         <v>144.97502770103799</v>
       </c>
       <c r="H62" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J62">
         <v>3</v>
@@ -3903,9 +3991,9 @@
         <v>84.646464646464651</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:13">
       <c r="A63" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B63" s="1">
         <f t="shared" si="0"/>
@@ -3915,10 +4003,10 @@
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E63" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F63">
         <v>-37.811457071394358</v>
@@ -3927,10 +4015,10 @@
         <v>144.98330902173689</v>
       </c>
       <c r="H63" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I63" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J63">
         <v>3</v>
@@ -3946,9 +4034,9 @@
         <v>85.454545454545453</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:13">
       <c r="A64" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B64" s="1">
         <f t="shared" si="0"/>
@@ -3958,10 +4046,10 @@
         <v>30</v>
       </c>
       <c r="D64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E64" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F64">
         <v>-37.829463346138489</v>
@@ -3970,10 +4058,10 @@
         <v>144.9970989578641</v>
       </c>
       <c r="H64" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I64" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J64">
         <v>2.5</v>
@@ -3989,9 +4077,9 @@
         <v>83.333333333333343</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:13">
       <c r="A65" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B65" s="1">
         <f t="shared" si="0"/>
@@ -4001,10 +4089,10 @@
         <v>30</v>
       </c>
       <c r="D65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E65" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F65">
         <v>-37.804407650985858</v>
@@ -4013,10 +4101,10 @@
         <v>144.9616612554934</v>
       </c>
       <c r="H65" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I65" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J65">
         <v>3</v>
@@ -4032,9 +4120,9 @@
         <v>86.666666666666671</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:13">
       <c r="A66" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B66" s="1">
         <f t="shared" si="0"/>
@@ -4044,10 +4132,10 @@
         <v>30</v>
       </c>
       <c r="D66" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E66" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F66">
         <v>-37.813368543612263</v>
@@ -4056,10 +4144,10 @@
         <v>144.97026450222339</v>
       </c>
       <c r="H66" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I66" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J66">
         <v>3</v>
@@ -4075,9 +4163,9 @@
         <v>85.858585858585855</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:13">
       <c r="A67" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B67" s="1">
         <f t="shared" si="0"/>
@@ -4087,10 +4175,10 @@
         <v>35</v>
       </c>
       <c r="D67" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E67" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F67">
         <v>-37.814618478807297</v>
@@ -4099,10 +4187,10 @@
         <v>144.97316429335001</v>
       </c>
       <c r="H67" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I67" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J67">
         <v>2.5</v>
@@ -4118,9 +4206,9 @@
         <v>83.535353535353536</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:13">
       <c r="A68" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B68" s="1">
         <f t="shared" si="0"/>
@@ -4130,10 +4218,10 @@
         <v>30</v>
       </c>
       <c r="D68" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E68" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F68">
         <v>-37.805952496044398</v>
@@ -4142,10 +4230,10 @@
         <v>144.984659053293</v>
       </c>
       <c r="H68" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I68" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J68">
         <v>2</v>
@@ -4161,22 +4249,22 @@
         <v>86.464646464646464</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:13">
       <c r="A69" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B69" s="1">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D69" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E69" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F69">
         <v>-37.813026238043904</v>
@@ -4185,10 +4273,10 @@
         <v>144.968406913411</v>
       </c>
       <c r="H69" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I69" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J69">
         <v>3</v>
@@ -4204,9 +4292,9 @@
         <v>85.050505050505052</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:13">
       <c r="A70" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B70" s="1">
         <f t="shared" si="0"/>
@@ -4216,10 +4304,10 @@
         <v>30</v>
       </c>
       <c r="D70" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F70">
         <v>-37.8059369769489</v>
@@ -4228,10 +4316,10 @@
         <v>144.98169239010099</v>
       </c>
       <c r="H70" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I70" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J70">
         <v>2.5</v>
@@ -4247,9 +4335,9 @@
         <v>83.939393939393938</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:13">
       <c r="A71" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B71" s="1">
         <f t="shared" si="0"/>
@@ -4259,10 +4347,10 @@
         <v>30</v>
       </c>
       <c r="D71" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E71" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F71">
         <v>-37.806169203803798</v>
@@ -4271,10 +4359,10 @@
         <v>144.97923370039601</v>
       </c>
       <c r="H71" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I71" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J71">
         <v>3</v>
@@ -4290,9 +4378,9 @@
         <v>81.414141414141412</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:13">
       <c r="A72" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B72" s="1">
         <f t="shared" si="0"/>
@@ -4302,10 +4390,10 @@
         <v>27</v>
       </c>
       <c r="D72" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F72">
         <v>-37.812681827366497</v>
@@ -4314,10 +4402,10 @@
         <v>144.97233693923599</v>
       </c>
       <c r="H72" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I72" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J72">
         <v>3.5</v>
@@ -4333,9 +4421,9 @@
         <v>83.535353535353536</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:13">
       <c r="A73" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B73" s="1">
         <f t="shared" si="0"/>
@@ -4345,10 +4433,10 @@
         <v>30</v>
       </c>
       <c r="D73" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E73" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F73">
         <v>-37.813540274691697</v>
@@ -4357,10 +4445,10 @@
         <v>144.96991551298299</v>
       </c>
       <c r="H73" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I73" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J73">
         <v>2</v>
@@ -4376,22 +4464,22 @@
         <v>84.848484848484844</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:13">
       <c r="A74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B74" s="1">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D74" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E74" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F74">
         <v>-37.808710505112401</v>
@@ -4400,10 +4488,10 @@
         <v>144.96177636627201</v>
       </c>
       <c r="H74" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I74" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J74">
         <v>3</v>
@@ -4417,6 +4505,393 @@
       <c r="M74" s="1">
         <f t="shared" si="1"/>
         <v>86.060606060606062</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" t="s">
+        <v>268</v>
+      </c>
+      <c r="B75" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C75" t="s">
+        <v>294</v>
+      </c>
+      <c r="D75" t="s">
+        <v>142</v>
+      </c>
+      <c r="E75" t="s">
+        <v>269</v>
+      </c>
+      <c r="F75">
+        <v>-37.809500060417299</v>
+      </c>
+      <c r="G75">
+        <v>144.96812236477001</v>
+      </c>
+      <c r="H75" t="s">
+        <v>270</v>
+      </c>
+      <c r="I75" t="s">
+        <v>145</v>
+      </c>
+      <c r="J75">
+        <v>3</v>
+      </c>
+      <c r="K75">
+        <v>85</v>
+      </c>
+      <c r="L75">
+        <v>88</v>
+      </c>
+      <c r="M75" s="1">
+        <f t="shared" si="1"/>
+        <v>84.040404040404042</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" t="s">
+        <v>272</v>
+      </c>
+      <c r="B76" s="1">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="C76" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76" t="s">
+        <v>139</v>
+      </c>
+      <c r="E76" t="s">
+        <v>273</v>
+      </c>
+      <c r="F76">
+        <v>-37.810465163416197</v>
+      </c>
+      <c r="G76">
+        <v>144.96623814569</v>
+      </c>
+      <c r="H76" t="s">
+        <v>271</v>
+      </c>
+      <c r="I76" t="s">
+        <v>159</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="K76">
+        <v>92</v>
+      </c>
+      <c r="L76">
+        <v>85</v>
+      </c>
+      <c r="M76" s="1">
+        <f t="shared" si="1"/>
+        <v>88.080808080808083</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" t="s">
+        <v>276</v>
+      </c>
+      <c r="B77" s="1">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="C77" t="s">
+        <v>167</v>
+      </c>
+      <c r="D77" t="s">
+        <v>139</v>
+      </c>
+      <c r="E77" t="s">
+        <v>277</v>
+      </c>
+      <c r="F77">
+        <v>-37.813019335403801</v>
+      </c>
+      <c r="G77">
+        <v>144.956459818919</v>
+      </c>
+      <c r="H77" t="s">
+        <v>275</v>
+      </c>
+      <c r="I77" t="s">
+        <v>159</v>
+      </c>
+      <c r="J77">
+        <v>2</v>
+      </c>
+      <c r="K77">
+        <v>84</v>
+      </c>
+      <c r="L77">
+        <v>82</v>
+      </c>
+      <c r="M77" s="1">
+        <f t="shared" si="1"/>
+        <v>82.020202020202021</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78" t="s">
+        <v>278</v>
+      </c>
+      <c r="B78" s="1">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C78" t="s">
+        <v>27</v>
+      </c>
+      <c r="D78" t="s">
+        <v>142</v>
+      </c>
+      <c r="E78" t="s">
+        <v>279</v>
+      </c>
+      <c r="F78">
+        <v>-37.816426526917503</v>
+      </c>
+      <c r="G78">
+        <v>144.97037504374299</v>
+      </c>
+      <c r="H78" t="s">
+        <v>280</v>
+      </c>
+      <c r="I78" t="s">
+        <v>215</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="K78">
+        <v>88</v>
+      </c>
+      <c r="L78">
+        <v>85</v>
+      </c>
+      <c r="M78" s="1">
+        <f t="shared" si="1"/>
+        <v>85.656565656565647</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
+      <c r="A79" t="s">
+        <v>282</v>
+      </c>
+      <c r="B79" s="1">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="C79" t="s">
+        <v>29</v>
+      </c>
+      <c r="D79" t="s">
+        <v>139</v>
+      </c>
+      <c r="E79" t="s">
+        <v>283</v>
+      </c>
+      <c r="F79">
+        <v>-37.8152002851226</v>
+      </c>
+      <c r="G79">
+        <v>144.96136334146499</v>
+      </c>
+      <c r="H79" t="s">
+        <v>281</v>
+      </c>
+      <c r="I79" t="s">
+        <v>145</v>
+      </c>
+      <c r="J79">
+        <v>4</v>
+      </c>
+      <c r="K79">
+        <v>90</v>
+      </c>
+      <c r="L79">
+        <v>90</v>
+      </c>
+      <c r="M79" s="1">
+        <f t="shared" si="1"/>
+        <v>86.868686868686879</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" t="s">
+        <v>284</v>
+      </c>
+      <c r="B80" s="1">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="C80" t="s">
+        <v>30</v>
+      </c>
+      <c r="D80" t="s">
+        <v>140</v>
+      </c>
+      <c r="E80" t="s">
+        <v>285</v>
+      </c>
+      <c r="F80">
+        <v>-37.815779532549897</v>
+      </c>
+      <c r="G80">
+        <v>144.96960098282099</v>
+      </c>
+      <c r="H80" t="s">
+        <v>286</v>
+      </c>
+      <c r="I80" t="s">
+        <v>145</v>
+      </c>
+      <c r="J80">
+        <v>5</v>
+      </c>
+      <c r="K80">
+        <v>95</v>
+      </c>
+      <c r="L80">
+        <v>92</v>
+      </c>
+      <c r="M80" s="1">
+        <f t="shared" si="1"/>
+        <v>89.696969696969703</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" t="s">
+        <v>287</v>
+      </c>
+      <c r="B81" s="1">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="C81" t="s">
+        <v>33</v>
+      </c>
+      <c r="D81" t="s">
+        <v>139</v>
+      </c>
+      <c r="E81" t="s">
+        <v>288</v>
+      </c>
+      <c r="F81">
+        <v>-37.809626553882602</v>
+      </c>
+      <c r="G81">
+        <v>144.961589310172</v>
+      </c>
+      <c r="H81" t="s">
+        <v>289</v>
+      </c>
+      <c r="I81" t="s">
+        <v>159</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81">
+        <v>93</v>
+      </c>
+      <c r="L81">
+        <v>87</v>
+      </c>
+      <c r="M81" s="1">
+        <f t="shared" si="1"/>
+        <v>89.494949494949495</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" t="s">
+        <v>290</v>
+      </c>
+      <c r="B82" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C82" t="s">
+        <v>291</v>
+      </c>
+      <c r="D82" t="s">
+        <v>139</v>
+      </c>
+      <c r="E82" t="s">
+        <v>292</v>
+      </c>
+      <c r="F82">
+        <v>-37.848659012346097</v>
+      </c>
+      <c r="G82">
+        <v>144.99349974737601</v>
+      </c>
+      <c r="H82" t="s">
+        <v>293</v>
+      </c>
+      <c r="I82" t="s">
+        <v>145</v>
+      </c>
+      <c r="J82">
+        <v>3</v>
+      </c>
+      <c r="K82">
+        <v>87</v>
+      </c>
+      <c r="L82">
+        <v>86</v>
+      </c>
+      <c r="M82" s="1">
+        <f t="shared" si="1"/>
+        <v>84.444444444444443</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" t="s">
+        <v>295</v>
+      </c>
+      <c r="B83" s="1">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="C83" t="s">
+        <v>297</v>
+      </c>
+      <c r="D83" t="s">
+        <v>142</v>
+      </c>
+      <c r="E83" t="s">
+        <v>298</v>
+      </c>
+      <c r="F83">
+        <v>-37.817613367172598</v>
+      </c>
+      <c r="G83">
+        <v>144.99203753217199</v>
+      </c>
+      <c r="H83" t="s">
+        <v>296</v>
+      </c>
+      <c r="I83" t="s">
+        <v>145</v>
+      </c>
+      <c r="J83">
+        <v>4</v>
+      </c>
+      <c r="K83">
+        <v>92</v>
+      </c>
+      <c r="L83">
+        <v>92</v>
+      </c>
+      <c r="M83" s="1">
+        <f t="shared" si="1"/>
+        <v>88.888888888888886</v>
       </c>
     </row>
   </sheetData>

--- a/restaurants.xlsx
+++ b/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cc66a12418570ca/Desktop/Projects/MelbEats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{CB70CA7D-8960-4D3D-9F79-019573917788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CEA4FA9-7C9C-4C96-AF12-185872CF2CF6}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="8_{CB70CA7D-8960-4D3D-9F79-019573917788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A60E4A9-259E-4E51-9E28-83C0B7492405}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66D3B1C7-080B-42FC-A787-EF3F4D2CE89F}"/>
   </bookViews>
@@ -866,9 +866,6 @@
     <t>https://maps.app.goo.gl/XYFR8QQzXAbMXEn48</t>
   </si>
   <si>
-    <t>Paik's BBQ</t>
-  </si>
-  <si>
     <t>Chaotic but delicious Korean BBQ place. Highly recommend going with someone who knows what they are doing!</t>
   </si>
   <si>
@@ -923,9 +920,6 @@
     <t>English</t>
   </si>
   <si>
-    <t>Vlado's Charcoal Grill</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/4kYMxa5gFYCMwthWA</t>
   </si>
   <si>
@@ -933,6 +927,12 @@
   </si>
   <si>
     <t>Iconic steakhouse with unchanged minimal menu for 50 years. Great experience</t>
+  </si>
+  <si>
+    <t>Vlados Charcoal Grill</t>
+  </si>
+  <si>
+    <t>Paiks BBQ</t>
   </si>
 </sst>
 </file>
@@ -4516,7 +4516,7 @@
         <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D75" t="s">
         <v>142</v>
@@ -4595,7 +4595,7 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="B77" s="1">
         <f t="shared" si="0"/>
@@ -4608,7 +4608,7 @@
         <v>139</v>
       </c>
       <c r="E77" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F77">
         <v>-37.813019335403801</v>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B78" s="1">
         <f t="shared" si="0"/>
@@ -4651,7 +4651,7 @@
         <v>142</v>
       </c>
       <c r="E78" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F78">
         <v>-37.816426526917503</v>
@@ -4660,7 +4660,7 @@
         <v>144.97037504374299</v>
       </c>
       <c r="H78" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I78" t="s">
         <v>215</v>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B79" s="1">
         <f t="shared" si="0"/>
@@ -4694,7 +4694,7 @@
         <v>139</v>
       </c>
       <c r="E79" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F79">
         <v>-37.8152002851226</v>
@@ -4703,7 +4703,7 @@
         <v>144.96136334146499</v>
       </c>
       <c r="H79" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I79" t="s">
         <v>145</v>
@@ -4724,7 +4724,7 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B80" s="1">
         <f t="shared" si="0"/>
@@ -4737,7 +4737,7 @@
         <v>140</v>
       </c>
       <c r="E80" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F80">
         <v>-37.815779532549897</v>
@@ -4746,7 +4746,7 @@
         <v>144.96960098282099</v>
       </c>
       <c r="H80" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I80" t="s">
         <v>145</v>
@@ -4767,7 +4767,7 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B81" s="1">
         <f t="shared" si="0"/>
@@ -4780,7 +4780,7 @@
         <v>139</v>
       </c>
       <c r="E81" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F81">
         <v>-37.809626553882602</v>
@@ -4789,7 +4789,7 @@
         <v>144.961589310172</v>
       </c>
       <c r="H81" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I81" t="s">
         <v>159</v>
@@ -4810,20 +4810,20 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" t="s">
+        <v>289</v>
+      </c>
+      <c r="B82" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C82" t="s">
         <v>290</v>
-      </c>
-      <c r="B82" s="1">
-        <f t="shared" si="0"/>
-        <v>84</v>
-      </c>
-      <c r="C82" t="s">
-        <v>291</v>
       </c>
       <c r="D82" t="s">
         <v>139</v>
       </c>
       <c r="E82" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F82">
         <v>-37.848659012346097</v>
@@ -4832,7 +4832,7 @@
         <v>144.99349974737601</v>
       </c>
       <c r="H82" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I82" t="s">
         <v>145</v>
@@ -4853,20 +4853,20 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" t="s">
+        <v>297</v>
+      </c>
+      <c r="B83" s="1">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="C83" t="s">
         <v>295</v>
-      </c>
-      <c r="B83" s="1">
-        <f t="shared" si="0"/>
-        <v>89</v>
-      </c>
-      <c r="C83" t="s">
-        <v>297</v>
       </c>
       <c r="D83" t="s">
         <v>142</v>
       </c>
       <c r="E83" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F83">
         <v>-37.817613367172598</v>
@@ -4875,7 +4875,7 @@
         <v>144.99203753217199</v>
       </c>
       <c r="H83" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I83" t="s">
         <v>145</v>
